--- a/PLC_Siemens1200/RCV Tags.xlsx
+++ b/PLC_Siemens1200/RCV Tags.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lutsk\OneDrive\Рабочий стол\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\RCV-master\RCV-master\PLC_Siemens1200\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10E7DA63-7610-4C56-8D95-DE3C1FFBE483}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABE889BB-A830-4E0E-BF3F-3BF83278726C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="442">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="883" uniqueCount="460">
   <si>
     <t>Bool</t>
   </si>
@@ -336,12 +336,6 @@
     <t>HMI_CycleOn</t>
   </si>
   <si>
-    <t>HMI_ChlorModeOn</t>
-  </si>
-  <si>
-    <t>HMI_DeChlorModeOn</t>
-  </si>
-  <si>
     <t>HMI_ManualModeOn</t>
   </si>
   <si>
@@ -381,15 +375,9 @@
     <t>Alarms_Open1</t>
   </si>
   <si>
-    <t>Alarms_Close1</t>
-  </si>
-  <si>
     <t>Alarms_Open2</t>
   </si>
   <si>
-    <t>Alarms_Close2</t>
-  </si>
-  <si>
     <t>Alarms_RCV1Max</t>
   </si>
   <si>
@@ -795,9 +783,6 @@
     <t>Ввімкнення режиму хлорації</t>
   </si>
   <si>
-    <t>Ввімкнення режиму дехлорації</t>
-  </si>
-  <si>
     <t>Вимкнення звуку сирени</t>
   </si>
   <si>
@@ -825,18 +810,12 @@
     <t>Обнулити значення вагів</t>
   </si>
   <si>
-    <t>Аварія відкриття засувки 1</t>
-  </si>
-  <si>
     <t>Аварія закриття засувки 1</t>
   </si>
   <si>
     <t>Аварія відкриття засувки 2</t>
   </si>
   <si>
-    <t>Аварія закриття засувки 2</t>
-  </si>
-  <si>
     <t>Аварія високий рівень РЧВ1</t>
   </si>
   <si>
@@ -1360,6 +1339,81 @@
   </si>
   <si>
     <t>Вік птиці</t>
+  </si>
+  <si>
+    <t>Struct</t>
+  </si>
+  <si>
+    <t>ChlorConsumptionTable[0]</t>
+  </si>
+  <si>
+    <t>Таблиця для генерації аварії великої витрати хлору</t>
+  </si>
+  <si>
+    <t>.Day</t>
+  </si>
+  <si>
+    <t>День циклу</t>
+  </si>
+  <si>
+    <t>.MonitorTime</t>
+  </si>
+  <si>
+    <t>Час моніторингу, години</t>
+  </si>
+  <si>
+    <t>.Consumption</t>
+  </si>
+  <si>
+    <t>Максимальна витрата, літри</t>
+  </si>
+  <si>
+    <t>ChlorConsumptionTable[1]</t>
+  </si>
+  <si>
+    <t>ChlorConsumptionTable[2]</t>
+  </si>
+  <si>
+    <t>ChlorConsumptionTable[3]</t>
+  </si>
+  <si>
+    <t>680.8</t>
+  </si>
+  <si>
+    <t>DoserNotWork</t>
+  </si>
+  <si>
+    <t>Насос дозатор не працює</t>
+  </si>
+  <si>
+    <t>680.9</t>
+  </si>
+  <si>
+    <t>Chlor_AutoMode</t>
+  </si>
+  <si>
+    <t>Перемикач режиму роботи, 0 - ручне, 1 - авто</t>
+  </si>
+  <si>
+    <t>HMI_Chlor_ModeOn</t>
+  </si>
+  <si>
+    <t>HMI_Chlor_ChooseTank</t>
+  </si>
+  <si>
+    <t>Робота хлорації по резервуару: 0  - РЧВ1 1-РЧВ2</t>
+  </si>
+  <si>
+    <t>Alarms_ChlorLargeConsumption</t>
+  </si>
+  <si>
+    <t>Аварія велика витрата хлору</t>
+  </si>
+  <si>
+    <t>HMI_WeightAlarmReset</t>
+  </si>
+  <si>
+    <t>Скидання аварії споживання хлору, при натисканні імпульс</t>
   </si>
 </sst>
 </file>
@@ -1431,7 +1485,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1439,28 +1493,47 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="62">
+  <dxfs count="12">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -1563,16 +1636,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -1588,496 +1651,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2357,7 +1930,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F191"/>
+  <dimension ref="A1:F209"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" customWidth="1"/>
@@ -2370,19 +1943,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B1" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D1" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E1" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -2393,13 +1966,13 @@
         <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D2" t="s">
         <v>1</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -2410,13 +1983,13 @@
         <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="D3" t="s">
         <v>3</v>
       </c>
       <c r="E3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -2427,13 +2000,13 @@
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="D4" t="s">
         <v>5</v>
       </c>
       <c r="E4" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -2444,13 +2017,13 @@
         <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="D5" t="s">
         <v>7</v>
       </c>
       <c r="E5" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -2461,13 +2034,13 @@
         <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="D6" t="s">
         <v>8</v>
       </c>
       <c r="E6" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -2478,13 +2051,13 @@
         <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="D7" t="s">
         <v>9</v>
       </c>
       <c r="E7" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -2495,13 +2068,13 @@
         <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="D8" t="s">
         <v>10</v>
       </c>
       <c r="E8" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -2512,13 +2085,13 @@
         <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D9" t="s">
         <v>11</v>
       </c>
       <c r="E9" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -2529,13 +2102,13 @@
         <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D10" t="s">
         <v>12</v>
       </c>
       <c r="E10" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -2546,13 +2119,13 @@
         <v>6</v>
       </c>
       <c r="C11" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D11" t="s">
         <v>13</v>
       </c>
       <c r="E11" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -2563,13 +2136,13 @@
         <v>6</v>
       </c>
       <c r="C12" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D12" t="s">
         <v>14</v>
       </c>
       <c r="E12" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -2580,13 +2153,13 @@
         <v>6</v>
       </c>
       <c r="C13" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D13" t="s">
         <v>15</v>
       </c>
       <c r="E13" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -2597,13 +2170,13 @@
         <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="D14" t="s">
         <v>16</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -2614,13 +2187,13 @@
         <v>17</v>
       </c>
       <c r="C15" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="D15" t="s">
         <v>18</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -2631,13 +2204,13 @@
         <v>17</v>
       </c>
       <c r="C16" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="D16" t="s">
         <v>19</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -2648,13 +2221,13 @@
         <v>17</v>
       </c>
       <c r="C17" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="D17" t="s">
         <v>20</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -2665,13 +2238,13 @@
         <v>17</v>
       </c>
       <c r="C18" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D18" t="s">
         <v>21</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -2682,13 +2255,13 @@
         <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D19" t="s">
         <v>22</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -2699,13 +2272,13 @@
         <v>17</v>
       </c>
       <c r="C20" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D20" t="s">
         <v>23</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
@@ -2716,13 +2289,13 @@
         <v>17</v>
       </c>
       <c r="C21" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D21" t="s">
         <v>24</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
@@ -2733,13 +2306,13 @@
         <v>17</v>
       </c>
       <c r="C22" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D22" t="s">
         <v>25</v>
       </c>
       <c r="E22" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
@@ -2750,13 +2323,13 @@
         <v>17</v>
       </c>
       <c r="C23" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D23" t="s">
         <v>26</v>
       </c>
       <c r="E23" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
@@ -2767,13 +2340,13 @@
         <v>17</v>
       </c>
       <c r="C24" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D24" t="s">
         <v>27</v>
       </c>
       <c r="E24" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
@@ -2784,13 +2357,13 @@
         <v>17</v>
       </c>
       <c r="C25" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D25" t="s">
         <v>28</v>
       </c>
       <c r="E25" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
@@ -2801,13 +2374,13 @@
         <v>17</v>
       </c>
       <c r="C26" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D26" t="s">
         <v>29</v>
       </c>
       <c r="E26" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
@@ -2818,13 +2391,13 @@
         <v>17</v>
       </c>
       <c r="C27" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D27" t="s">
         <v>30</v>
       </c>
       <c r="E27" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
@@ -2835,13 +2408,13 @@
         <v>17</v>
       </c>
       <c r="C28" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D28" t="s">
         <v>31</v>
       </c>
       <c r="E28" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
@@ -2852,13 +2425,13 @@
         <v>17</v>
       </c>
       <c r="C29" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D29" t="s">
         <v>32</v>
       </c>
       <c r="E29" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
@@ -2869,13 +2442,13 @@
         <v>17</v>
       </c>
       <c r="C30" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D30" t="s">
         <v>33</v>
       </c>
       <c r="E30" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
@@ -2886,13 +2459,13 @@
         <v>17</v>
       </c>
       <c r="C31" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D31" t="s">
         <v>34</v>
       </c>
       <c r="E31" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
@@ -2903,13 +2476,13 @@
         <v>17</v>
       </c>
       <c r="C32" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D32" t="s">
         <v>35</v>
       </c>
       <c r="E32" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
@@ -2920,13 +2493,13 @@
         <v>17</v>
       </c>
       <c r="C33" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="D33" t="s">
         <v>36</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
@@ -2937,13 +2510,13 @@
         <v>17</v>
       </c>
       <c r="C34" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="D34" t="s">
         <v>37</v>
       </c>
       <c r="E34" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
@@ -2954,13 +2527,13 @@
         <v>17</v>
       </c>
       <c r="C35" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D35" t="s">
         <v>38</v>
       </c>
       <c r="E35" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
@@ -2971,13 +2544,13 @@
         <v>17</v>
       </c>
       <c r="C36" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D36" t="s">
         <v>39</v>
       </c>
       <c r="E36" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
@@ -2988,13 +2561,13 @@
         <v>17</v>
       </c>
       <c r="C37" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D37" t="s">
         <v>40</v>
       </c>
       <c r="E37" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
@@ -3002,16 +2575,16 @@
         <v>61</v>
       </c>
       <c r="B38" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C38" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D38" t="s">
         <v>41</v>
       </c>
       <c r="E38" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
@@ -3022,13 +2595,13 @@
         <v>17</v>
       </c>
       <c r="C39" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D39" t="s">
         <v>42</v>
       </c>
       <c r="E39" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
@@ -3039,13 +2612,13 @@
         <v>17</v>
       </c>
       <c r="C40" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D40" t="s">
         <v>43</v>
       </c>
       <c r="E40" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
@@ -3056,13 +2629,13 @@
         <v>17</v>
       </c>
       <c r="C41" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D41" t="s">
         <v>44</v>
       </c>
       <c r="E41" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
@@ -3070,16 +2643,16 @@
         <v>69</v>
       </c>
       <c r="B42" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C42" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D42" t="s">
         <v>45</v>
       </c>
       <c r="E42" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
@@ -3090,13 +2663,13 @@
         <v>17</v>
       </c>
       <c r="C43" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D43" t="s">
         <v>46</v>
       </c>
       <c r="E43" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
@@ -3107,13 +2680,13 @@
         <v>17</v>
       </c>
       <c r="C44" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D44" t="s">
         <v>47</v>
       </c>
       <c r="E44" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
@@ -3124,13 +2697,13 @@
         <v>17</v>
       </c>
       <c r="C45" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D45" t="s">
         <v>48</v>
       </c>
       <c r="E45" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
@@ -3138,16 +2711,16 @@
         <v>77</v>
       </c>
       <c r="B46" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C46" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D46" t="s">
         <v>49</v>
       </c>
       <c r="E46" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
@@ -3158,13 +2731,13 @@
         <v>17</v>
       </c>
       <c r="C47" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D47" t="s">
         <v>50</v>
       </c>
       <c r="E47" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
@@ -3175,13 +2748,13 @@
         <v>17</v>
       </c>
       <c r="C48" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D48" t="s">
         <v>51</v>
       </c>
       <c r="E48" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
@@ -3192,13 +2765,13 @@
         <v>17</v>
       </c>
       <c r="C49" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D49" t="s">
         <v>52</v>
       </c>
       <c r="E49" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
@@ -3206,16 +2779,16 @@
         <v>85</v>
       </c>
       <c r="B50" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C50" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D50" t="s">
         <v>53</v>
       </c>
       <c r="E50" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
@@ -3226,13 +2799,13 @@
         <v>17</v>
       </c>
       <c r="C51" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D51" t="s">
         <v>54</v>
       </c>
       <c r="E51" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
@@ -3243,13 +2816,13 @@
         <v>17</v>
       </c>
       <c r="C52" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D52" t="s">
         <v>55</v>
       </c>
       <c r="E52" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
@@ -3260,13 +2833,13 @@
         <v>17</v>
       </c>
       <c r="C53" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D53" t="s">
         <v>56</v>
       </c>
       <c r="E53" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
@@ -3274,16 +2847,16 @@
         <v>93</v>
       </c>
       <c r="B54" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C54" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D54" t="s">
         <v>57</v>
       </c>
       <c r="E54" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
@@ -3294,13 +2867,13 @@
         <v>17</v>
       </c>
       <c r="C55" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="D55" t="s">
         <v>58</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
@@ -3311,13 +2884,13 @@
         <v>17</v>
       </c>
       <c r="C56" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="D56" t="s">
         <v>59</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
@@ -3328,13 +2901,13 @@
         <v>17</v>
       </c>
       <c r="C57" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="D57" t="s">
         <v>60</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
@@ -3345,13 +2918,13 @@
         <v>17</v>
       </c>
       <c r="C58" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="D58" t="s">
         <v>61</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
@@ -3362,13 +2935,13 @@
         <v>17</v>
       </c>
       <c r="C59" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="D59" t="s">
         <v>62</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
@@ -3379,13 +2952,13 @@
         <v>17</v>
       </c>
       <c r="C60" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D60" t="s">
         <v>63</v>
       </c>
       <c r="E60" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
@@ -3396,13 +2969,13 @@
         <v>17</v>
       </c>
       <c r="C61" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D61" t="s">
         <v>64</v>
       </c>
       <c r="E61" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
@@ -3413,13 +2986,13 @@
         <v>17</v>
       </c>
       <c r="C62" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D62" t="s">
         <v>65</v>
       </c>
       <c r="E62" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
@@ -3430,13 +3003,13 @@
         <v>17</v>
       </c>
       <c r="C63" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D63" t="s">
         <v>66</v>
       </c>
       <c r="E63" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
@@ -3447,13 +3020,13 @@
         <v>17</v>
       </c>
       <c r="C64" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D64" t="s">
         <v>67</v>
       </c>
       <c r="E64" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
@@ -3464,13 +3037,13 @@
         <v>17</v>
       </c>
       <c r="C65" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D65" t="s">
         <v>68</v>
       </c>
       <c r="E65" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
@@ -3481,13 +3054,13 @@
         <v>17</v>
       </c>
       <c r="C66" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D66" t="s">
         <v>69</v>
       </c>
       <c r="E66" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
@@ -3498,13 +3071,13 @@
         <v>17</v>
       </c>
       <c r="C67" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D67" t="s">
         <v>70</v>
       </c>
       <c r="E67" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
@@ -3515,13 +3088,13 @@
         <v>17</v>
       </c>
       <c r="C68" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D68" t="s">
         <v>71</v>
       </c>
       <c r="E68" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
@@ -3532,13 +3105,13 @@
         <v>17</v>
       </c>
       <c r="C69" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D69" t="s">
         <v>72</v>
       </c>
       <c r="E69" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
@@ -3549,13 +3122,13 @@
         <v>17</v>
       </c>
       <c r="C70" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D70" t="s">
         <v>73</v>
       </c>
       <c r="E70" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
@@ -3566,13 +3139,13 @@
         <v>17</v>
       </c>
       <c r="C71" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="D71" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="E71" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
@@ -3583,13 +3156,13 @@
         <v>17</v>
       </c>
       <c r="C72" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="D72" t="s">
         <v>74</v>
       </c>
       <c r="E72" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
@@ -3600,13 +3173,13 @@
         <v>17</v>
       </c>
       <c r="C73" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D73" t="s">
         <v>75</v>
       </c>
       <c r="E73" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
@@ -3617,13 +3190,13 @@
         <v>17</v>
       </c>
       <c r="C74" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D74" t="s">
         <v>76</v>
       </c>
       <c r="E74" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
@@ -3634,30 +3207,30 @@
         <v>4</v>
       </c>
       <c r="C75" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D75" t="s">
         <v>77</v>
       </c>
       <c r="E75" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="B76" t="s">
         <v>0</v>
       </c>
       <c r="C76" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D76" t="s">
         <v>78</v>
       </c>
       <c r="E76" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
@@ -3668,13 +3241,13 @@
         <v>17</v>
       </c>
       <c r="C77" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D77" t="s">
         <v>79</v>
       </c>
       <c r="E77" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
@@ -3685,13 +3258,13 @@
         <v>17</v>
       </c>
       <c r="C78" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D78" t="s">
         <v>80</v>
       </c>
       <c r="E78" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
@@ -3702,13 +3275,13 @@
         <v>17</v>
       </c>
       <c r="C79" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D79" t="s">
         <v>81</v>
       </c>
       <c r="E79" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
@@ -3719,13 +3292,13 @@
         <v>17</v>
       </c>
       <c r="C80" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D80" t="s">
         <v>82</v>
       </c>
       <c r="E80" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
@@ -3736,13 +3309,13 @@
         <v>17</v>
       </c>
       <c r="C81" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D81" t="s">
         <v>83</v>
       </c>
       <c r="E81" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
@@ -3753,13 +3326,13 @@
         <v>17</v>
       </c>
       <c r="C82" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D82" t="s">
         <v>84</v>
       </c>
       <c r="E82" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
@@ -3770,13 +3343,13 @@
         <v>17</v>
       </c>
       <c r="C83" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D83" t="s">
         <v>85</v>
       </c>
       <c r="E83" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
@@ -3787,13 +3360,13 @@
         <v>17</v>
       </c>
       <c r="C84" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="D84" t="s">
         <v>86</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
@@ -3804,13 +3377,13 @@
         <v>17</v>
       </c>
       <c r="C85" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="D85" t="s">
         <v>87</v>
       </c>
       <c r="E85" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
@@ -3821,13 +3394,13 @@
         <v>17</v>
       </c>
       <c r="C86" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="D86" t="s">
         <v>88</v>
       </c>
       <c r="E86" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
@@ -3838,13 +3411,13 @@
         <v>17</v>
       </c>
       <c r="C87" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D87" t="s">
         <v>89</v>
       </c>
       <c r="E87" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
@@ -3855,13 +3428,13 @@
         <v>17</v>
       </c>
       <c r="C88" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D88" t="s">
         <v>90</v>
       </c>
       <c r="E88" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
@@ -3872,13 +3445,13 @@
         <v>17</v>
       </c>
       <c r="C89" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D89" t="s">
         <v>91</v>
       </c>
       <c r="E89" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
@@ -3889,13 +3462,13 @@
         <v>17</v>
       </c>
       <c r="C90" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D90" t="s">
         <v>92</v>
       </c>
       <c r="E90" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
@@ -3906,13 +3479,13 @@
         <v>17</v>
       </c>
       <c r="C91" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D91" t="s">
         <v>93</v>
       </c>
       <c r="E91" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
@@ -3923,13 +3496,13 @@
         <v>17</v>
       </c>
       <c r="C92" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D92" t="s">
         <v>94</v>
       </c>
       <c r="E92" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
@@ -3940,13 +3513,13 @@
         <v>17</v>
       </c>
       <c r="C93" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D93" t="s">
         <v>95</v>
       </c>
       <c r="E93" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
@@ -3957,13 +3530,13 @@
         <v>17</v>
       </c>
       <c r="C94" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="D94" t="s">
         <v>96</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
@@ -3974,13 +3547,13 @@
         <v>17</v>
       </c>
       <c r="C95" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="D95" t="s">
         <v>97</v>
       </c>
       <c r="E95" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
@@ -3991,557 +3564,557 @@
         <v>17</v>
       </c>
       <c r="C96" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="D96" t="s">
         <v>98</v>
       </c>
       <c r="E96" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B97" t="s">
         <v>0</v>
       </c>
       <c r="C97" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D97" t="s">
         <v>99</v>
       </c>
       <c r="E97" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A98" t="s">
-        <v>150</v>
-      </c>
-      <c r="B98" t="s">
+      <c r="A98" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="B98" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="C98" t="s">
-        <v>290</v>
-      </c>
-      <c r="D98" t="s">
-        <v>100</v>
-      </c>
-      <c r="E98" t="s">
-        <v>252</v>
+      <c r="C98" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="D98" s="11" t="s">
+        <v>453</v>
+      </c>
+      <c r="E98" s="11" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A99" t="s">
-        <v>151</v>
-      </c>
-      <c r="B99" t="s">
+      <c r="A99" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="B99" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="C99" t="s">
-        <v>290</v>
-      </c>
-      <c r="D99" t="s">
-        <v>101</v>
-      </c>
-      <c r="E99" t="s">
-        <v>253</v>
+      <c r="C99" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="D99" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="E99" s="11" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="100" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>152</v>
-      </c>
-      <c r="B100" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B100" t="s">
         <v>0</v>
       </c>
       <c r="C100" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>153</v>
-      </c>
-      <c r="B101" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B101" t="s">
         <v>0</v>
       </c>
       <c r="C101" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D101" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E101" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
     </row>
     <row r="102" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>154</v>
-      </c>
-      <c r="B102" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B102" t="s">
         <v>0</v>
       </c>
       <c r="C102" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
     </row>
     <row r="103" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>155</v>
-      </c>
-      <c r="B103" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B103" t="s">
         <v>0</v>
       </c>
       <c r="C103" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B104" t="s">
         <v>0</v>
       </c>
       <c r="C104" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D104" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E104" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B105" t="s">
         <v>0</v>
       </c>
       <c r="C105" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D105" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E105" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B106" t="s">
         <v>0</v>
       </c>
       <c r="C106" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D106" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E106" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B107" t="s">
         <v>0</v>
       </c>
       <c r="C107" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D107" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E107" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B108" t="s">
         <v>0</v>
       </c>
       <c r="C108" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D108" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E108" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B109" t="s">
         <v>0</v>
       </c>
       <c r="C109" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D109" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E109" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B110" t="s">
         <v>0</v>
       </c>
       <c r="C110" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D110" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E110" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B111" t="s">
         <v>0</v>
       </c>
       <c r="C111" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D111" t="s">
+        <v>111</v>
+      </c>
+      <c r="E111" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A112" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="B112" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C112" s="13" t="s">
+        <v>283</v>
+      </c>
+      <c r="D112" s="13" t="s">
+        <v>458</v>
+      </c>
+      <c r="E112" s="13" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A113" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="B113" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C113" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="D113" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="E113" s="12" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A114" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="B114" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C114" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="D114" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="E111" t="s">
+      <c r="E114" s="12" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A115" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="B115" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C115" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="D115" s="12" t="s">
+        <v>456</v>
+      </c>
+      <c r="E115" s="12" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A116" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="B116" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C116" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="D116" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="E116" s="12" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A117" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="B117" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C117" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="D117" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="E117" s="12" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A118" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="B118" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C118" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="D118" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="E118" s="12" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A112" t="s">
-        <v>148</v>
-      </c>
-      <c r="B112" t="s">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A119" s="12" t="s">
+        <v>335</v>
+      </c>
+      <c r="B119" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C112" t="s">
-        <v>291</v>
-      </c>
-      <c r="D112" t="s">
-        <v>114</v>
-      </c>
-      <c r="E112" t="s">
+      <c r="C119" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="D119" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="E119" s="12" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A113" t="s">
-        <v>163</v>
-      </c>
-      <c r="B113" t="s">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A120" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="B120" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C113" t="s">
-        <v>291</v>
-      </c>
-      <c r="D113" t="s">
-        <v>115</v>
-      </c>
-      <c r="E113" t="s">
+      <c r="C120" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="D120" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="E120" s="12" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A114" t="s">
-        <v>164</v>
-      </c>
-      <c r="B114" t="s">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A121" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="B121" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C114" t="s">
-        <v>291</v>
-      </c>
-      <c r="D114" t="s">
-        <v>116</v>
-      </c>
-      <c r="E114" t="s">
+      <c r="C121" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="D121" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="E121" s="12" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A115" t="s">
-        <v>165</v>
-      </c>
-      <c r="B115" t="s">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A122" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="B122" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C115" t="s">
-        <v>291</v>
-      </c>
-      <c r="D115" t="s">
-        <v>117</v>
-      </c>
-      <c r="E115" t="s">
+      <c r="C122" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="D122" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="E122" s="12" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A116" t="s">
-        <v>166</v>
-      </c>
-      <c r="B116" t="s">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A123" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="B123" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C116" t="s">
-        <v>291</v>
-      </c>
-      <c r="D116" t="s">
-        <v>118</v>
-      </c>
-      <c r="E116" t="s">
+      <c r="C123" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="D123" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="E123" s="12" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A117" t="s">
-        <v>167</v>
-      </c>
-      <c r="B117" t="s">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A124" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="B124" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C117" t="s">
-        <v>291</v>
-      </c>
-      <c r="D117" t="s">
-        <v>119</v>
-      </c>
-      <c r="E117" t="s">
+      <c r="C124" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="D124" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="E124" s="12" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A118" t="s">
-        <v>168</v>
-      </c>
-      <c r="B118" t="s">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A125" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="B125" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C118" t="s">
-        <v>291</v>
-      </c>
-      <c r="D118" t="s">
-        <v>120</v>
-      </c>
-      <c r="E118" t="s">
+      <c r="C125" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="D125" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="E125" s="12" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A119" t="s">
-        <v>342</v>
-      </c>
-      <c r="B119" t="s">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A126" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="B126" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C119" t="s">
-        <v>291</v>
-      </c>
-      <c r="D119" t="s">
-        <v>121</v>
-      </c>
-      <c r="E119" t="s">
+      <c r="C126" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="D126" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="E126" s="12" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A120" t="s">
-        <v>343</v>
-      </c>
-      <c r="B120" t="s">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A127" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="B127" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C120" t="s">
-        <v>291</v>
-      </c>
-      <c r="D120" t="s">
-        <v>122</v>
-      </c>
-      <c r="E120" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A121" t="s">
-        <v>157</v>
-      </c>
-      <c r="B121" t="s">
+      <c r="C127" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="D127" s="12" t="s">
+        <v>353</v>
+      </c>
+      <c r="E127" s="12" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A128" s="12" t="s">
+        <v>358</v>
+      </c>
+      <c r="B128" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C121" t="s">
-        <v>291</v>
-      </c>
-      <c r="D121" t="s">
-        <v>123</v>
-      </c>
-      <c r="E121" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A122" t="s">
-        <v>158</v>
-      </c>
-      <c r="B122" t="s">
-        <v>0</v>
-      </c>
-      <c r="C122" t="s">
-        <v>291</v>
-      </c>
-      <c r="D122" t="s">
-        <v>124</v>
-      </c>
-      <c r="E122" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A123" t="s">
-        <v>159</v>
-      </c>
-      <c r="B123" t="s">
-        <v>0</v>
-      </c>
-      <c r="C123" t="s">
-        <v>291</v>
-      </c>
-      <c r="D123" t="s">
-        <v>125</v>
-      </c>
-      <c r="E123" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A124" t="s">
-        <v>160</v>
-      </c>
-      <c r="B124" t="s">
-        <v>0</v>
-      </c>
-      <c r="C124" t="s">
-        <v>291</v>
-      </c>
-      <c r="D124" t="s">
-        <v>126</v>
-      </c>
-      <c r="E124" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A125" t="s">
-        <v>161</v>
-      </c>
-      <c r="B125" t="s">
-        <v>0</v>
-      </c>
-      <c r="C125" t="s">
-        <v>291</v>
-      </c>
-      <c r="D125" t="s">
-        <v>127</v>
-      </c>
-      <c r="E125" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A126" t="s">
-        <v>162</v>
-      </c>
-      <c r="B126" t="s">
-        <v>0</v>
-      </c>
-      <c r="C126" t="s">
-        <v>291</v>
-      </c>
-      <c r="D126" t="s">
-        <v>128</v>
-      </c>
-      <c r="E126" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A127" t="s">
-        <v>364</v>
-      </c>
-      <c r="B127" t="s">
-        <v>0</v>
-      </c>
-      <c r="C127" t="s">
-        <v>291</v>
-      </c>
-      <c r="D127" t="s">
-        <v>360</v>
-      </c>
-      <c r="E127" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A128" t="s">
-        <v>365</v>
-      </c>
-      <c r="B128" t="s">
-        <v>0</v>
-      </c>
-      <c r="C128" t="s">
-        <v>291</v>
-      </c>
-      <c r="D128" t="s">
-        <v>361</v>
-      </c>
-      <c r="E128" t="s">
-        <v>363</v>
+      <c r="C128" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="D128" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="E128" s="12" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.3">
@@ -4552,13 +4125,13 @@
         <v>17</v>
       </c>
       <c r="C129" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D129" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E129" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.3">
@@ -4569,13 +4142,13 @@
         <v>17</v>
       </c>
       <c r="C130" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D130" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E130" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.3">
@@ -4583,33 +4156,33 @@
         <v>213</v>
       </c>
       <c r="B131" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C131" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D131" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E131" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="B132" t="s">
         <v>0</v>
       </c>
       <c r="C132" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="D132" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E132" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.3">
@@ -4620,183 +4193,183 @@
         <v>17</v>
       </c>
       <c r="C133" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="D133" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="E133" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="B134" t="s">
         <v>0</v>
       </c>
       <c r="C134" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="D134" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E134" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="B135" t="s">
         <v>0</v>
       </c>
       <c r="C135" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="D135" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E135" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="B136" t="s">
         <v>0</v>
       </c>
       <c r="C136" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="D136" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E136" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="B137" t="s">
         <v>0</v>
       </c>
       <c r="C137" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="D137" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E137" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="B138" t="s">
         <v>0</v>
       </c>
       <c r="C138" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="D138" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E138" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="B139" t="s">
         <v>0</v>
       </c>
       <c r="C139" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="D139" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E139" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="B140" t="s">
         <v>0</v>
       </c>
       <c r="C140" t="s">
-        <v>291</v>
-      </c>
-      <c r="D140" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="E140" s="4" t="s">
-        <v>321</v>
+        <v>284</v>
+      </c>
+      <c r="D140" t="s">
+        <v>297</v>
+      </c>
+      <c r="E140" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="B141" t="s">
         <v>0</v>
       </c>
       <c r="C141" t="s">
-        <v>291</v>
-      </c>
-      <c r="D141" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="E141" s="4" t="s">
-        <v>322</v>
+        <v>284</v>
+      </c>
+      <c r="D141" t="s">
+        <v>298</v>
+      </c>
+      <c r="E141" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A142" s="6" t="s">
-        <v>369</v>
-      </c>
-      <c r="B142" s="6" t="s">
+      <c r="A142" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="B142" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C142" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="D142" s="6" t="s">
-        <v>367</v>
-      </c>
-      <c r="E142" s="6" t="s">
-        <v>372</v>
+      <c r="C142" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="D142" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="E142" s="5" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A143" s="6" t="s">
-        <v>371</v>
-      </c>
-      <c r="B143" s="6" t="s">
+      <c r="A143" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="B143" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C143" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="D143" s="6" t="s">
-        <v>368</v>
-      </c>
-      <c r="E143" s="6" t="s">
-        <v>370</v>
+      <c r="C143" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="D143" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="E143" s="5" t="s">
+        <v>363</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.3">
@@ -4807,13 +4380,13 @@
         <v>17</v>
       </c>
       <c r="C144" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="D144" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="E144" t="s">
-        <v>417</v>
+        <v>410</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.3">
@@ -4824,13 +4397,13 @@
         <v>17</v>
       </c>
       <c r="C145" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="D145" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="E145" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.3">
@@ -4841,13 +4414,13 @@
         <v>17</v>
       </c>
       <c r="C146" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D146" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="E146" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.3">
@@ -4858,13 +4431,13 @@
         <v>17</v>
       </c>
       <c r="C147" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D147" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="E147" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.3">
@@ -4875,13 +4448,13 @@
         <v>17</v>
       </c>
       <c r="C148" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D148" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="E148" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.3">
@@ -4892,196 +4465,196 @@
         <v>17</v>
       </c>
       <c r="C149" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D149" t="s">
+        <v>303</v>
+      </c>
+      <c r="E149" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A150" s="4">
+        <v>255</v>
+      </c>
+      <c r="B150" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C150" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="D150" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="E150" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="F150" s="8" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A151" s="4">
+        <v>257</v>
+      </c>
+      <c r="B151" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C151" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="D151" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="E151" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="F151" s="8"/>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A152" s="4">
+        <v>259</v>
+      </c>
+      <c r="B152" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C152" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="D152" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="E152" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="F152" s="8"/>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A153" s="4">
+        <v>261</v>
+      </c>
+      <c r="B153" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C153" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="D153" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="E153" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="F153" s="8"/>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A154" s="4">
+        <v>263</v>
+      </c>
+      <c r="B154" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C154" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="D154" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="E154" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="F154" s="8"/>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A155" s="4">
+        <v>265</v>
+      </c>
+      <c r="B155" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C155" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="D155" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="E155" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="F155" s="8"/>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A156" s="4">
+        <v>267</v>
+      </c>
+      <c r="B156" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C156" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="D156" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="E149" t="s">
+      <c r="E156" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="F156" s="8"/>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A157" s="4">
+        <v>269</v>
+      </c>
+      <c r="B157" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C157" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="D157" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="E157" s="4" t="s">
         <v>327</v>
       </c>
-    </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A150" s="5">
-        <v>255</v>
-      </c>
-      <c r="B150" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C150" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="D150" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="E150" s="5" t="s">
-        <v>337</v>
-      </c>
-      <c r="F150" s="7" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A151" s="5">
-        <v>257</v>
-      </c>
-      <c r="B151" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C151" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="D151" s="5" t="s">
+      <c r="F157" s="8"/>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A158" s="4">
+        <v>271</v>
+      </c>
+      <c r="B158" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C158" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="D158" s="4" t="s">
         <v>312</v>
       </c>
-      <c r="E151" s="5" t="s">
+      <c r="E158" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="F158" s="8"/>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A159" s="4">
+        <v>273</v>
+      </c>
+      <c r="B159" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C159" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="D159" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="E159" s="4" t="s">
         <v>329</v>
       </c>
-      <c r="F151" s="7"/>
-    </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A152" s="5">
-        <v>259</v>
-      </c>
-      <c r="B152" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C152" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="D152" s="5" t="s">
-        <v>313</v>
-      </c>
-      <c r="E152" s="5" t="s">
-        <v>330</v>
-      </c>
-      <c r="F152" s="7"/>
-    </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A153" s="5">
-        <v>261</v>
-      </c>
-      <c r="B153" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C153" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="D153" s="5" t="s">
-        <v>314</v>
-      </c>
-      <c r="E153" s="5" t="s">
-        <v>331</v>
-      </c>
-      <c r="F153" s="7"/>
-    </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A154" s="5">
-        <v>263</v>
-      </c>
-      <c r="B154" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C154" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="D154" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="E154" s="5" t="s">
-        <v>332</v>
-      </c>
-      <c r="F154" s="7"/>
-    </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A155" s="5">
-        <v>265</v>
-      </c>
-      <c r="B155" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C155" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="D155" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="E155" s="5" t="s">
-        <v>328</v>
-      </c>
-      <c r="F155" s="7"/>
-    </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A156" s="5">
-        <v>267</v>
-      </c>
-      <c r="B156" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C156" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="D156" s="5" t="s">
-        <v>317</v>
-      </c>
-      <c r="E156" s="5" t="s">
-        <v>333</v>
-      </c>
-      <c r="F156" s="7"/>
-    </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A157" s="5">
-        <v>269</v>
-      </c>
-      <c r="B157" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C157" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="D157" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="E157" s="5" t="s">
-        <v>334</v>
-      </c>
-      <c r="F157" s="7"/>
-    </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A158" s="5">
-        <v>271</v>
-      </c>
-      <c r="B158" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C158" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="D158" s="5" t="s">
-        <v>319</v>
-      </c>
-      <c r="E158" s="5" t="s">
-        <v>335</v>
-      </c>
-      <c r="F158" s="7"/>
-    </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A159" s="5">
-        <v>273</v>
-      </c>
-      <c r="B159" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C159" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="D159" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="E159" s="5" t="s">
-        <v>336</v>
-      </c>
-      <c r="F159" s="7"/>
+      <c r="F159" s="8"/>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A160">
@@ -5090,14 +4663,14 @@
       <c r="B160" t="s">
         <v>17</v>
       </c>
-      <c r="C160" s="5" t="s">
-        <v>290</v>
+      <c r="C160" s="4" t="s">
+        <v>283</v>
       </c>
       <c r="D160" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="E160" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.3">
@@ -5107,14 +4680,14 @@
       <c r="B161" t="s">
         <v>17</v>
       </c>
-      <c r="C161" s="5" t="s">
-        <v>290</v>
+      <c r="C161" s="4" t="s">
+        <v>283</v>
       </c>
       <c r="D161" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="E161" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.3">
@@ -5122,510 +4695,802 @@
         <v>279</v>
       </c>
       <c r="B162" t="s">
-        <v>132</v>
-      </c>
-      <c r="C162" s="5" t="s">
-        <v>290</v>
+        <v>128</v>
+      </c>
+      <c r="C162" s="4" t="s">
+        <v>283</v>
       </c>
       <c r="D162" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="E162" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A163" s="8" t="s">
+      <c r="A163" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="B163" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C163" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="D163" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="E163" s="6" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A164" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="B164" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C164" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="D164" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="E164" s="6" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A165" s="6">
+        <v>284</v>
+      </c>
+      <c r="B165" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C165" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="D165" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="E165" s="6" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A166" s="6">
+        <v>286</v>
+      </c>
+      <c r="B166" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C166" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="D166" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="E166" s="6" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A167" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="B167" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C167" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="D167" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="E167" s="6" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A168" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="B168" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C168" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="D168" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="E168" s="6" t="s">
         <v>395</v>
       </c>
-      <c r="B163" s="8" t="s">
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A169" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="B169" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C163" s="8" t="s">
-        <v>290</v>
-      </c>
-      <c r="D163" s="8" t="s">
+      <c r="C169" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="D169" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="E169" s="6" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A170" s="6">
+        <v>289</v>
+      </c>
+      <c r="B170" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C170" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="D170" s="6" t="s">
         <v>373</v>
       </c>
-      <c r="E163" s="8" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A164" s="8" t="s">
-        <v>396</v>
-      </c>
-      <c r="B164" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="C164" s="8" t="s">
-        <v>290</v>
-      </c>
-      <c r="D164" s="8" t="s">
+      <c r="E170" s="6" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A171" s="6">
+        <v>291</v>
+      </c>
+      <c r="B171" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C171" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="D171" s="6" t="s">
         <v>374</v>
       </c>
-      <c r="E164" s="8" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A165" s="8">
-        <v>284</v>
-      </c>
-      <c r="B165" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C165" s="8" t="s">
-        <v>291</v>
-      </c>
-      <c r="D165" s="8" t="s">
+      <c r="E171" s="6" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A172" s="6">
+        <v>293</v>
+      </c>
+      <c r="B172" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="C172" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="D172" s="6" t="s">
         <v>375</v>
       </c>
-      <c r="E165" s="8" t="s">
+      <c r="E172" s="6" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A166" s="8">
-        <v>286</v>
-      </c>
-      <c r="B166" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C166" s="8" t="s">
-        <v>291</v>
-      </c>
-      <c r="D166" s="8" t="s">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A173" s="6">
+        <v>295</v>
+      </c>
+      <c r="B173" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C173" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="D173" s="6" t="s">
         <v>376</v>
       </c>
-      <c r="E166" s="8" t="s">
+      <c r="E173" s="6" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A167" s="8" t="s">
-        <v>397</v>
-      </c>
-      <c r="B167" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="C167" s="8" t="s">
-        <v>291</v>
-      </c>
-      <c r="D167" s="8" t="s">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A174" s="6">
+        <v>297</v>
+      </c>
+      <c r="B174" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="C174" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="D174" s="6" t="s">
         <v>377</v>
       </c>
-      <c r="E167" s="8" t="s">
+      <c r="E174" s="6" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A175" s="6">
+        <v>327</v>
+      </c>
+      <c r="B175" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="C175" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="D175" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="E175" s="6" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A168" s="8" t="s">
-        <v>398</v>
-      </c>
-      <c r="B168" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="C168" s="8" t="s">
-        <v>291</v>
-      </c>
-      <c r="D168" s="8" t="s">
-        <v>378</v>
-      </c>
-      <c r="E168" s="8" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A169" s="8" t="s">
-        <v>399</v>
-      </c>
-      <c r="B169" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="C169" s="8" t="s">
-        <v>290</v>
-      </c>
-      <c r="D169" s="8" t="s">
-        <v>379</v>
-      </c>
-      <c r="E169" s="8" t="s">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A176" s="6">
+        <v>357</v>
+      </c>
+      <c r="B176" s="6" t="s">
+        <v>381</v>
+      </c>
+      <c r="C176" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="D176" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="E176" s="6" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A170" s="8">
-        <v>289</v>
-      </c>
-      <c r="B170" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C170" s="8" t="s">
-        <v>290</v>
-      </c>
-      <c r="D170" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="E170" s="8" t="s">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A177" s="6">
+        <v>387</v>
+      </c>
+      <c r="B177" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="C177" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="D177" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="E177" s="6" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A178" s="6">
+        <v>447</v>
+      </c>
+      <c r="B178" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="C178" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="D178" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="E178" s="6" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A171" s="8">
-        <v>291</v>
-      </c>
-      <c r="B171" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C171" s="8" t="s">
-        <v>290</v>
-      </c>
-      <c r="D171" s="8" t="s">
-        <v>381</v>
-      </c>
-      <c r="E171" s="8" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A172" s="8">
-        <v>293</v>
-      </c>
-      <c r="B172" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="C172" s="8" t="s">
-        <v>290</v>
-      </c>
-      <c r="D172" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="E172" s="8" t="s">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A179" s="6">
+        <v>507</v>
+      </c>
+      <c r="B179" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="C179" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="D179" s="6" t="s">
+        <v>385</v>
+      </c>
+      <c r="E179" s="6" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A173" s="8">
-        <v>295</v>
-      </c>
-      <c r="B173" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C173" s="8" t="s">
-        <v>290</v>
-      </c>
-      <c r="D173" s="8" t="s">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A180" s="6">
+        <v>567</v>
+      </c>
+      <c r="B180" s="6" t="s">
         <v>383</v>
       </c>
-      <c r="E173" s="8" t="s">
+      <c r="C180" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="D180" s="6" t="s">
+        <v>386</v>
+      </c>
+      <c r="E180" s="6" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A174" s="8">
-        <v>297</v>
-      </c>
-      <c r="B174" s="8" t="s">
-        <v>385</v>
-      </c>
-      <c r="C174" s="8" t="s">
-        <v>291</v>
-      </c>
-      <c r="D174" s="8" t="s">
-        <v>384</v>
-      </c>
-      <c r="E174" s="8" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A175" s="8">
-        <v>327</v>
-      </c>
-      <c r="B175" s="8" t="s">
-        <v>385</v>
-      </c>
-      <c r="C175" s="8" t="s">
-        <v>291</v>
-      </c>
-      <c r="D175" s="8" t="s">
-        <v>386</v>
-      </c>
-      <c r="E175" s="8" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A176" s="8">
-        <v>357</v>
-      </c>
-      <c r="B176" s="8" t="s">
-        <v>388</v>
-      </c>
-      <c r="C176" s="8" t="s">
-        <v>291</v>
-      </c>
-      <c r="D176" s="8" t="s">
-        <v>387</v>
-      </c>
-      <c r="E176" s="8" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A177" s="8">
-        <v>387</v>
-      </c>
-      <c r="B177" s="8" t="s">
-        <v>390</v>
-      </c>
-      <c r="C177" s="8" t="s">
-        <v>291</v>
-      </c>
-      <c r="D177" s="8" t="s">
-        <v>389</v>
-      </c>
-      <c r="E177" s="8" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A178" s="8">
-        <v>447</v>
-      </c>
-      <c r="B178" s="8" t="s">
-        <v>390</v>
-      </c>
-      <c r="C178" s="8" t="s">
-        <v>291</v>
-      </c>
-      <c r="D178" s="8" t="s">
-        <v>391</v>
-      </c>
-      <c r="E178" s="8" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A179" s="8">
-        <v>507</v>
-      </c>
-      <c r="B179" s="8" t="s">
-        <v>390</v>
-      </c>
-      <c r="C179" s="8" t="s">
-        <v>291</v>
-      </c>
-      <c r="D179" s="8" t="s">
-        <v>392</v>
-      </c>
-      <c r="E179" s="8" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A180" s="8">
-        <v>567</v>
-      </c>
-      <c r="B180" s="8" t="s">
-        <v>390</v>
-      </c>
-      <c r="C180" s="8" t="s">
-        <v>291</v>
-      </c>
-      <c r="D180" s="8" t="s">
-        <v>393</v>
-      </c>
-      <c r="E180" s="8" t="s">
-        <v>415</v>
-      </c>
-    </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A181" s="9">
+      <c r="A181" s="7">
         <f>274/2</f>
         <v>137</v>
       </c>
-      <c r="B181" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C181" s="9" t="s">
-        <v>290</v>
-      </c>
-      <c r="D181" s="9" t="s">
+      <c r="B181" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C181" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="D181" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="E181" s="7" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A182" s="7">
+        <v>141</v>
+      </c>
+      <c r="B182" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C182" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="D182" s="7" t="s">
+        <v>412</v>
+      </c>
+      <c r="E182" s="7" t="s">
         <v>418</v>
       </c>
-      <c r="E181" s="9" t="s">
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A183" s="7">
+        <v>145</v>
+      </c>
+      <c r="B183" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C183" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="D183" s="7" t="s">
+        <v>413</v>
+      </c>
+      <c r="E183" s="7" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A184" s="7">
+        <v>147</v>
+      </c>
+      <c r="B184" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C184" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="D184" s="7" t="s">
+        <v>414</v>
+      </c>
+      <c r="E184" s="7" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A185" s="7">
+        <v>151</v>
+      </c>
+      <c r="B185" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C185" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="D185" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="E185" s="7" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A186" s="7">
+        <v>155</v>
+      </c>
+      <c r="B186" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C186" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="D186" s="7" t="s">
+        <v>416</v>
+      </c>
+      <c r="E186" s="7" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A187" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="B187" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="C187" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="D187" s="7" t="s">
+        <v>423</v>
+      </c>
+      <c r="E187" s="7" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A188" s="7">
+        <v>628</v>
+      </c>
+      <c r="B188" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="C188" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="D188" s="7" t="s">
         <v>424</v>
       </c>
-    </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A182" s="9">
-        <v>141</v>
-      </c>
-      <c r="B182" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C182" s="9" t="s">
-        <v>291</v>
-      </c>
-      <c r="D182" s="9" t="s">
-        <v>419</v>
-      </c>
-      <c r="E182" s="9" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A183" s="9">
-        <v>145</v>
-      </c>
-      <c r="B183" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C183" s="9" t="s">
-        <v>291</v>
-      </c>
-      <c r="D183" s="9" t="s">
-        <v>420</v>
-      </c>
-      <c r="E183" s="9" t="s">
+      <c r="E188" s="7" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A189" s="7">
+        <v>638</v>
+      </c>
+      <c r="B189" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C189" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="D189" s="7" t="s">
         <v>426</v>
       </c>
-    </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A184" s="9">
-        <v>147</v>
-      </c>
-      <c r="B184" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C184" s="9" t="s">
-        <v>290</v>
-      </c>
-      <c r="D184" s="9" t="s">
-        <v>421</v>
-      </c>
-      <c r="E184" s="9" t="s">
+      <c r="E189" s="7" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A190" s="7">
+        <v>640</v>
+      </c>
+      <c r="B190" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C190" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="D190" s="7" t="s">
         <v>427</v>
       </c>
-    </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A185" s="9">
-        <v>151</v>
-      </c>
-      <c r="B185" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C185" s="9" t="s">
-        <v>291</v>
-      </c>
-      <c r="D185" s="9" t="s">
-        <v>422</v>
-      </c>
-      <c r="E185" s="9" t="s">
+      <c r="E190" s="7" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A191" s="7">
+        <v>642</v>
+      </c>
+      <c r="B191" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C191" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="D191" s="7" t="s">
         <v>428</v>
       </c>
-    </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A186" s="9">
-        <v>155</v>
-      </c>
-      <c r="B186" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C186" s="9" t="s">
-        <v>291</v>
-      </c>
-      <c r="D186" s="9" t="s">
-        <v>423</v>
-      </c>
-      <c r="E186" s="9" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A187" s="9" t="s">
+      <c r="E191" s="7" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A192" s="10">
+        <v>660</v>
+      </c>
+      <c r="B192" s="10" t="s">
+        <v>435</v>
+      </c>
+      <c r="C192" s="10"/>
+      <c r="D192" s="10" t="s">
         <v>436</v>
       </c>
-      <c r="B187" s="9" t="s">
+      <c r="E192" s="10" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A193" s="10">
+        <v>660</v>
+      </c>
+      <c r="B193" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="C193" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="D193" s="10" t="s">
+        <v>438</v>
+      </c>
+      <c r="E193" s="10" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A194" s="9">
+        <v>661</v>
+      </c>
+      <c r="B194" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C194" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="D194" s="9" t="s">
+        <v>440</v>
+      </c>
+      <c r="E194" s="9" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A195" s="9">
+        <v>663</v>
+      </c>
+      <c r="B195" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C195" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="D195" s="9" t="s">
+        <v>442</v>
+      </c>
+      <c r="E195" s="9" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A196" s="9">
+        <v>665</v>
+      </c>
+      <c r="B196" s="9" t="s">
+        <v>435</v>
+      </c>
+      <c r="C196" s="10"/>
+      <c r="D196" s="9" t="s">
+        <v>444</v>
+      </c>
+      <c r="E196" s="9"/>
+    </row>
+    <row r="197" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A197" s="9">
+        <v>665</v>
+      </c>
+      <c r="B197" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C197" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="D197" s="10" t="s">
+        <v>438</v>
+      </c>
+      <c r="E197" s="10" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A198" s="9">
+        <v>666</v>
+      </c>
+      <c r="B198" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C198" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="D198" s="9" t="s">
+        <v>440</v>
+      </c>
+      <c r="E198" s="9" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A199" s="9">
+        <v>668</v>
+      </c>
+      <c r="B199" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C199" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="D199" s="9" t="s">
+        <v>442</v>
+      </c>
+      <c r="E199" s="9" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A200" s="9">
+        <v>670</v>
+      </c>
+      <c r="B200" s="9" t="s">
+        <v>435</v>
+      </c>
+      <c r="C200" s="10"/>
+      <c r="D200" s="9" t="s">
+        <v>445</v>
+      </c>
+      <c r="E200" s="9"/>
+    </row>
+    <row r="201" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A201" s="9">
+        <v>670</v>
+      </c>
+      <c r="B201" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C201" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="D201" s="10" t="s">
+        <v>438</v>
+      </c>
+      <c r="E201" s="10" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A202" s="9">
+        <v>671</v>
+      </c>
+      <c r="B202" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C202" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="D202" s="9" t="s">
+        <v>440</v>
+      </c>
+      <c r="E202" s="9" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A203" s="9">
+        <v>673</v>
+      </c>
+      <c r="B203" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C203" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="D203" s="9" t="s">
+        <v>442</v>
+      </c>
+      <c r="E203" s="9" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A204" s="9">
+        <v>675</v>
+      </c>
+      <c r="B204" s="9" t="s">
+        <v>435</v>
+      </c>
+      <c r="C204" s="10"/>
+      <c r="D204" s="9" t="s">
+        <v>446</v>
+      </c>
+      <c r="E204" s="9"/>
+    </row>
+    <row r="205" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A205" s="9">
+        <v>675</v>
+      </c>
+      <c r="B205" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C205" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="D205" s="10" t="s">
+        <v>438</v>
+      </c>
+      <c r="E205" s="10" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A206" s="9">
+        <v>676</v>
+      </c>
+      <c r="B206" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C206" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="D206" s="9" t="s">
+        <v>440</v>
+      </c>
+      <c r="E206" s="9" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A207" s="9">
+        <v>678</v>
+      </c>
+      <c r="B207" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C207" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="D207" s="9" t="s">
+        <v>442</v>
+      </c>
+      <c r="E207" s="9" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A208" s="9" t="s">
+        <v>447</v>
+      </c>
+      <c r="B208" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C187" s="9" t="s">
-        <v>291</v>
-      </c>
-      <c r="D187" s="9" t="s">
-        <v>430</v>
-      </c>
-      <c r="E187" s="9" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A188" s="9">
-        <v>628</v>
-      </c>
-      <c r="B188" s="9" t="s">
-        <v>432</v>
-      </c>
-      <c r="C188" s="9" t="s">
-        <v>291</v>
-      </c>
-      <c r="D188" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="E188" s="9" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A189" s="9">
-        <v>638</v>
-      </c>
-      <c r="B189" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C189" s="9" t="s">
-        <v>291</v>
-      </c>
-      <c r="D189" s="9" t="s">
-        <v>433</v>
-      </c>
-      <c r="E189" s="9" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A190" s="9">
-        <v>640</v>
-      </c>
-      <c r="B190" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C190" s="9" t="s">
-        <v>291</v>
-      </c>
-      <c r="D190" s="9" t="s">
-        <v>434</v>
-      </c>
-      <c r="E190" s="9" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A191" s="9">
-        <v>642</v>
-      </c>
-      <c r="B191" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="C191" s="9" t="s">
-        <v>291</v>
-      </c>
-      <c r="D191" s="9" t="s">
-        <v>435</v>
-      </c>
-      <c r="E191" s="9" t="s">
-        <v>441</v>
+      <c r="C208" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="D208" s="10" t="s">
+        <v>448</v>
+      </c>
+      <c r="E208" s="9" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A209" s="9" t="s">
+        <v>450</v>
+      </c>
+      <c r="B209" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C209" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="D209" s="10" t="s">
+        <v>451</v>
+      </c>
+      <c r="E209" s="9" t="s">
+        <v>452</v>
       </c>
     </row>
   </sheetData>
@@ -5633,244 +5498,52 @@
     <mergeCell ref="F150:F159"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="C1:C70 B71 C72:C126 B127:C128 B145:B159 C129:C141 B142:C142 C143:D143 D166:D180 D188 B181:B186 C194:C1048576 B191">
-    <cfRule type="containsText" dxfId="61" priority="63" operator="containsText" text="View">
-      <formula>NOT(ISERROR(SEARCH("View",B1)))</formula>
+  <conditionalFormatting sqref="B71 B127:C128 C129:C141 B142:C142 B145:B159 D166:D180 B181:B186 B191 C194:C1048576">
+    <cfRule type="containsText" dxfId="11" priority="64" operator="containsText" text="Set">
+      <formula>NOT(ISERROR(SEARCH("Set",B71)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="60" priority="64" operator="containsText" text="Set">
-      <formula>NOT(ISERROR(SEARCH("Set",B1)))</formula>
+    <cfRule type="containsText" dxfId="10" priority="63" operator="containsText" text="View">
+      <formula>NOT(ISERROR(SEARCH("View",B71)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B143">
-    <cfRule type="containsText" dxfId="59" priority="59" operator="containsText" text="View">
+  <conditionalFormatting sqref="B143:D143">
+    <cfRule type="containsText" dxfId="9" priority="59" operator="containsText" text="View">
       <formula>NOT(ISERROR(SEARCH("View",B143)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="58" priority="60" operator="containsText" text="Set">
+    <cfRule type="containsText" dxfId="8" priority="60" operator="containsText" text="Set">
       <formula>NOT(ISERROR(SEARCH("Set",B143)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C145">
-    <cfRule type="containsText" dxfId="57" priority="57" operator="containsText" text="View">
-      <formula>NOT(ISERROR(SEARCH("View",C145)))</formula>
+  <conditionalFormatting sqref="C1:C126">
+    <cfRule type="containsText" dxfId="7" priority="27" operator="containsText" text="View">
+      <formula>NOT(ISERROR(SEARCH("View",C1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="56" priority="58" operator="containsText" text="Set">
-      <formula>NOT(ISERROR(SEARCH("Set",C145)))</formula>
+    <cfRule type="containsText" dxfId="6" priority="28" operator="containsText" text="Set">
+      <formula>NOT(ISERROR(SEARCH("Set",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C146">
-    <cfRule type="containsText" dxfId="55" priority="55" operator="containsText" text="View">
-      <formula>NOT(ISERROR(SEARCH("View",C146)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="54" priority="56" operator="containsText" text="Set">
-      <formula>NOT(ISERROR(SEARCH("Set",C146)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C147">
-    <cfRule type="containsText" dxfId="53" priority="53" operator="containsText" text="View">
-      <formula>NOT(ISERROR(SEARCH("View",C147)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="52" priority="54" operator="containsText" text="Set">
-      <formula>NOT(ISERROR(SEARCH("Set",C147)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C148">
-    <cfRule type="containsText" dxfId="51" priority="51" operator="containsText" text="View">
-      <formula>NOT(ISERROR(SEARCH("View",C148)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="50" priority="52" operator="containsText" text="Set">
-      <formula>NOT(ISERROR(SEARCH("Set",C148)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C149">
-    <cfRule type="containsText" dxfId="49" priority="49" operator="containsText" text="View">
-      <formula>NOT(ISERROR(SEARCH("View",C149)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="48" priority="50" operator="containsText" text="Set">
-      <formula>NOT(ISERROR(SEARCH("Set",C149)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C150">
-    <cfRule type="containsText" dxfId="47" priority="47" operator="containsText" text="View">
-      <formula>NOT(ISERROR(SEARCH("View",C150)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="46" priority="48" operator="containsText" text="Set">
-      <formula>NOT(ISERROR(SEARCH("Set",C150)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C151">
-    <cfRule type="containsText" dxfId="45" priority="45" operator="containsText" text="View">
-      <formula>NOT(ISERROR(SEARCH("View",C151)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="44" priority="46" operator="containsText" text="Set">
-      <formula>NOT(ISERROR(SEARCH("Set",C151)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C152">
-    <cfRule type="containsText" dxfId="43" priority="43" operator="containsText" text="View">
-      <formula>NOT(ISERROR(SEARCH("View",C152)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="42" priority="44" operator="containsText" text="Set">
-      <formula>NOT(ISERROR(SEARCH("Set",C152)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C153">
-    <cfRule type="containsText" dxfId="41" priority="41" operator="containsText" text="View">
-      <formula>NOT(ISERROR(SEARCH("View",C153)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="40" priority="42" operator="containsText" text="Set">
-      <formula>NOT(ISERROR(SEARCH("Set",C153)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C154">
-    <cfRule type="containsText" dxfId="39" priority="39" operator="containsText" text="View">
-      <formula>NOT(ISERROR(SEARCH("View",C154)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="38" priority="40" operator="containsText" text="Set">
-      <formula>NOT(ISERROR(SEARCH("Set",C154)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C155">
-    <cfRule type="containsText" dxfId="37" priority="37" operator="containsText" text="View">
-      <formula>NOT(ISERROR(SEARCH("View",C155)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="36" priority="38" operator="containsText" text="Set">
-      <formula>NOT(ISERROR(SEARCH("Set",C155)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C156">
-    <cfRule type="containsText" dxfId="35" priority="35" operator="containsText" text="View">
-      <formula>NOT(ISERROR(SEARCH("View",C156)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="34" priority="36" operator="containsText" text="Set">
-      <formula>NOT(ISERROR(SEARCH("Set",C156)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C157">
-    <cfRule type="containsText" dxfId="33" priority="33" operator="containsText" text="View">
-      <formula>NOT(ISERROR(SEARCH("View",C157)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="32" priority="34" operator="containsText" text="Set">
-      <formula>NOT(ISERROR(SEARCH("Set",C157)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C158 C160 C162">
-    <cfRule type="containsText" dxfId="31" priority="31" operator="containsText" text="View">
-      <formula>NOT(ISERROR(SEARCH("View",C158)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="30" priority="32" operator="containsText" text="Set">
-      <formula>NOT(ISERROR(SEARCH("Set",C158)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C159 C161 C163:C180">
-    <cfRule type="containsText" dxfId="29" priority="29" operator="containsText" text="View">
-      <formula>NOT(ISERROR(SEARCH("View",C159)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="28" priority="30" operator="containsText" text="Set">
-      <formula>NOT(ISERROR(SEARCH("Set",C159)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C71">
-    <cfRule type="containsText" dxfId="27" priority="27" operator="containsText" text="View">
-      <formula>NOT(ISERROR(SEARCH("View",C71)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="26" priority="28" operator="containsText" text="Set">
-      <formula>NOT(ISERROR(SEARCH("Set",C71)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C144">
-    <cfRule type="containsText" dxfId="25" priority="25" operator="containsText" text="View">
+  <conditionalFormatting sqref="C144:C187">
+    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="View">
       <formula>NOT(ISERROR(SEARCH("View",C144)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="24" priority="26" operator="containsText" text="Set">
+    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="Set">
       <formula>NOT(ISERROR(SEARCH("Set",C144)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C181">
-    <cfRule type="containsText" dxfId="23" priority="23" operator="containsText" text="View">
-      <formula>NOT(ISERROR(SEARCH("View",C181)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="22" priority="24" operator="containsText" text="Set">
-      <formula>NOT(ISERROR(SEARCH("Set",C181)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C184">
-    <cfRule type="containsText" dxfId="21" priority="21" operator="containsText" text="View">
-      <formula>NOT(ISERROR(SEARCH("View",C184)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="20" priority="22" operator="containsText" text="Set">
-      <formula>NOT(ISERROR(SEARCH("Set",C184)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C182">
-    <cfRule type="containsText" dxfId="19" priority="19" operator="containsText" text="View">
-      <formula>NOT(ISERROR(SEARCH("View",C182)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="18" priority="20" operator="containsText" text="Set">
-      <formula>NOT(ISERROR(SEARCH("Set",C182)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C183">
-    <cfRule type="containsText" dxfId="17" priority="17" operator="containsText" text="View">
-      <formula>NOT(ISERROR(SEARCH("View",C183)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="16" priority="18" operator="containsText" text="Set">
-      <formula>NOT(ISERROR(SEARCH("Set",C183)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C185">
-    <cfRule type="containsText" dxfId="15" priority="15" operator="containsText" text="View">
-      <formula>NOT(ISERROR(SEARCH("View",C185)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="14" priority="16" operator="containsText" text="Set">
-      <formula>NOT(ISERROR(SEARCH("Set",C185)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C186">
-    <cfRule type="containsText" dxfId="13" priority="13" operator="containsText" text="View">
-      <formula>NOT(ISERROR(SEARCH("View",C186)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="14" operator="containsText" text="Set">
-      <formula>NOT(ISERROR(SEARCH("Set",C186)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C188">
-    <cfRule type="containsText" dxfId="9" priority="9" operator="containsText" text="View">
-      <formula>NOT(ISERROR(SEARCH("View",C188)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="10" operator="containsText" text="Set">
-      <formula>NOT(ISERROR(SEARCH("Set",C188)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C189">
-    <cfRule type="containsText" dxfId="7" priority="7" operator="containsText" text="View">
+  <conditionalFormatting sqref="C189:C191">
+    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="View">
       <formula>NOT(ISERROR(SEARCH("View",C189)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="8" operator="containsText" text="Set">
+    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="Set">
       <formula>NOT(ISERROR(SEARCH("Set",C189)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C190">
-    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="View">
-      <formula>NOT(ISERROR(SEARCH("View",C190)))</formula>
+  <conditionalFormatting sqref="C188:D188">
+    <cfRule type="containsText" dxfId="1" priority="9" operator="containsText" text="View">
+      <formula>NOT(ISERROR(SEARCH("View",C188)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="6" operator="containsText" text="Set">
-      <formula>NOT(ISERROR(SEARCH("Set",C190)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C191">
-    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="View">
-      <formula>NOT(ISERROR(SEARCH("View",C191)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="Set">
-      <formula>NOT(ISERROR(SEARCH("Set",C191)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C187">
-    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="View">
-      <formula>NOT(ISERROR(SEARCH("View",C187)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="Set">
-      <formula>NOT(ISERROR(SEARCH("Set",C187)))</formula>
+    <cfRule type="containsText" dxfId="0" priority="10" operator="containsText" text="Set">
+      <formula>NOT(ISERROR(SEARCH("Set",C188)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/PLC_Siemens1200/RCV Tags.xlsx
+++ b/PLC_Siemens1200/RCV Tags.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\RCV-master\RCV-master\PLC_Siemens1200\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\RCV\PLC_Siemens1200\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABE889BB-A830-4E0E-BF3F-3BF83278726C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C88DC42-FAD3-4603-B58C-CB0E13F5F1B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="883" uniqueCount="460">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="938" uniqueCount="488">
   <si>
     <t>Bool</t>
   </si>
@@ -1414,6 +1414,90 @@
   </si>
   <si>
     <t>Скидання аварії споживання хлору, при натисканні імпульс</t>
+  </si>
+  <si>
+    <t>Chloration_ChooseCounter</t>
+  </si>
+  <si>
+    <t>WaterCounterOut_DailyValue</t>
+  </si>
+  <si>
+    <t>WaterCounterOut_TotalValue</t>
+  </si>
+  <si>
+    <t>WaterCounterOut_PulseValue</t>
+  </si>
+  <si>
+    <t>WaterCounterOut_Consumption</t>
+  </si>
+  <si>
+    <t>AbsoluteDosing</t>
+  </si>
+  <si>
+    <t>ProportionalDosingExternal</t>
+  </si>
+  <si>
+    <t>WorkMode</t>
+  </si>
+  <si>
+    <t>Doser1Productivity</t>
+  </si>
+  <si>
+    <t>Doser2Productivity</t>
+  </si>
+  <si>
+    <t>SystemProductivity</t>
+  </si>
+  <si>
+    <t>Alarms</t>
+  </si>
+  <si>
+    <t>1361.3</t>
+  </si>
+  <si>
+    <t>Вибір лічильника для дозування 0 - вхідний, 1 - вихідний</t>
+  </si>
+  <si>
+    <t>1489.1</t>
+  </si>
+  <si>
+    <t>1489.2</t>
+  </si>
+  <si>
+    <t>Режим абсолютного дозування</t>
+  </si>
+  <si>
+    <t>Режим пропорційного дозування</t>
+  </si>
+  <si>
+    <t>0 аварій нема, якщо більше 0 аварія</t>
+  </si>
+  <si>
+    <t>Продуктивність системи, г/год</t>
+  </si>
+  <si>
+    <t>Продуктивність дозатора 1, л/год</t>
+  </si>
+  <si>
+    <t>Продуктивність дозатора 2, л/год</t>
+  </si>
+  <si>
+    <t>Задача пропорційного дозування діоксиду, мг/л</t>
+  </si>
+  <si>
+    <t>Задача абсолютного дозування діоксиду, г/год</t>
+  </si>
+  <si>
+    <t>Вихідний лічильник (новий) значення за день, м3</t>
+  </si>
+  <si>
+    <t>Вихідний лічильник (новий) значення за весь час, м3</t>
+  </si>
+  <si>
+    <t>Вихідний лічильник (новий) вага імпульса, м3</t>
+  </si>
+  <si>
+    <t>Вихідний лічильник (новий) миттєва витрата, м3/год</t>
   </si>
 </sst>
 </file>
@@ -1480,7 +1564,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="7" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1512,28 +1596,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="20">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -1636,6 +1719,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -1651,6 +1744,76 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1930,7 +2093,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F209"/>
+  <dimension ref="A1:F227"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" customWidth="1"/>
@@ -1942,3608 +2105,3879 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="3" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C2" t="s">
-        <v>283</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="C2" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="7" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3">
+      <c r="A3" s="3">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C3" t="s">
-        <v>284</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="C3" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="3" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4">
+      <c r="A4" s="3">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C4" t="s">
-        <v>284</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="C4" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="3" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5">
+      <c r="A5" s="3">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C5" t="s">
-        <v>284</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="C5" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="3" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6">
+      <c r="A6" s="3">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C6" t="s">
-        <v>284</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="C6" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="3" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7">
+      <c r="A7" s="3">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C7" t="s">
-        <v>284</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="C7" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="3" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8">
+      <c r="A8" s="3">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C8" t="s">
-        <v>284</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="C8" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="3" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9">
+      <c r="A9" s="3">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C9" t="s">
-        <v>283</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="C9" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="3" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10">
+      <c r="A10" s="3">
         <v>9</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C10" t="s">
-        <v>283</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="C10" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="3" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11">
+      <c r="A11" s="3">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C11" t="s">
-        <v>283</v>
-      </c>
-      <c r="D11" t="s">
+      <c r="C11" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="3" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12">
+      <c r="A12" s="3">
         <v>11</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C12" t="s">
-        <v>283</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="C12" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="3" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13">
+      <c r="A13" s="3">
         <v>12</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C13" t="s">
-        <v>283</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="C13" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="3" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14">
+      <c r="A14" s="3">
         <v>13</v>
       </c>
-      <c r="B14" t="s">
-        <v>17</v>
-      </c>
-      <c r="C14" t="s">
-        <v>284</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="B14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E14" s="7" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15">
+      <c r="A15" s="3">
         <v>15</v>
       </c>
-      <c r="B15" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" t="s">
-        <v>284</v>
-      </c>
-      <c r="D15" t="s">
+      <c r="B15" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="E15" s="7" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <v>17</v>
-      </c>
-      <c r="B16" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" t="s">
-        <v>284</v>
-      </c>
-      <c r="D16" t="s">
+      <c r="A16" s="3">
+        <v>17</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="E16" s="7" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17">
+      <c r="A17" s="3">
         <v>19</v>
       </c>
-      <c r="B17" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17" t="s">
-        <v>284</v>
-      </c>
-      <c r="D17" t="s">
+      <c r="B17" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="E17" s="7" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18">
+      <c r="A18" s="3">
         <v>21</v>
       </c>
-      <c r="B18" t="s">
-        <v>17</v>
-      </c>
-      <c r="C18" t="s">
-        <v>283</v>
-      </c>
-      <c r="D18" t="s">
+      <c r="B18" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E18" s="8" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19">
+      <c r="A19" s="3">
         <v>23</v>
       </c>
-      <c r="B19" t="s">
-        <v>17</v>
-      </c>
-      <c r="C19" t="s">
-        <v>283</v>
-      </c>
-      <c r="D19" t="s">
+      <c r="B19" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E19" s="8" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20">
+      <c r="A20" s="3">
         <v>25</v>
       </c>
-      <c r="B20" t="s">
-        <v>17</v>
-      </c>
-      <c r="C20" t="s">
-        <v>283</v>
-      </c>
-      <c r="D20" t="s">
+      <c r="B20" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="E20" s="8" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21">
+      <c r="A21" s="3">
         <v>27</v>
       </c>
-      <c r="B21" t="s">
-        <v>17</v>
-      </c>
-      <c r="C21" t="s">
-        <v>283</v>
-      </c>
-      <c r="D21" t="s">
+      <c r="B21" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="E21" s="8" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22">
+      <c r="A22" s="3">
         <v>29</v>
       </c>
-      <c r="B22" t="s">
-        <v>17</v>
-      </c>
-      <c r="C22" t="s">
-        <v>283</v>
-      </c>
-      <c r="D22" t="s">
+      <c r="B22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E22" s="3" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23">
+      <c r="A23" s="3">
         <v>31</v>
       </c>
-      <c r="B23" t="s">
-        <v>17</v>
-      </c>
-      <c r="C23" t="s">
-        <v>283</v>
-      </c>
-      <c r="D23" t="s">
+      <c r="B23" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D23" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E23" s="3" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24">
+      <c r="A24" s="3">
         <v>33</v>
       </c>
-      <c r="B24" t="s">
-        <v>17</v>
-      </c>
-      <c r="C24" t="s">
-        <v>283</v>
-      </c>
-      <c r="D24" t="s">
+      <c r="B24" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E24" s="3" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25">
+      <c r="A25" s="3">
         <v>35</v>
       </c>
-      <c r="B25" t="s">
-        <v>17</v>
-      </c>
-      <c r="C25" t="s">
-        <v>283</v>
-      </c>
-      <c r="D25" t="s">
+      <c r="B25" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D25" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E25" s="3" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26">
+      <c r="A26" s="3">
         <v>37</v>
       </c>
-      <c r="B26" t="s">
-        <v>17</v>
-      </c>
-      <c r="C26" t="s">
-        <v>283</v>
-      </c>
-      <c r="D26" t="s">
+      <c r="B26" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E26" t="s">
+      <c r="E26" s="3" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27">
+      <c r="A27" s="3">
         <v>39</v>
       </c>
-      <c r="B27" t="s">
-        <v>17</v>
-      </c>
-      <c r="C27" t="s">
-        <v>283</v>
-      </c>
-      <c r="D27" t="s">
+      <c r="B27" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D27" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E27" s="3" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28">
+      <c r="A28" s="3">
         <v>41</v>
       </c>
-      <c r="B28" t="s">
-        <v>17</v>
-      </c>
-      <c r="C28" t="s">
-        <v>283</v>
-      </c>
-      <c r="D28" t="s">
+      <c r="B28" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D28" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E28" t="s">
+      <c r="E28" s="3" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29">
+      <c r="A29" s="3">
         <v>43</v>
       </c>
-      <c r="B29" t="s">
-        <v>17</v>
-      </c>
-      <c r="C29" t="s">
-        <v>283</v>
-      </c>
-      <c r="D29" t="s">
+      <c r="B29" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D29" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E29" t="s">
+      <c r="E29" s="3" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30">
+      <c r="A30" s="3">
         <v>45</v>
       </c>
-      <c r="B30" t="s">
-        <v>17</v>
-      </c>
-      <c r="C30" t="s">
-        <v>283</v>
-      </c>
-      <c r="D30" t="s">
+      <c r="B30" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D30" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E30" t="s">
+      <c r="E30" s="3" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31">
+      <c r="A31" s="3">
         <v>47</v>
       </c>
-      <c r="B31" t="s">
-        <v>17</v>
-      </c>
-      <c r="C31" t="s">
-        <v>283</v>
-      </c>
-      <c r="D31" t="s">
+      <c r="B31" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D31" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E31" s="3" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32">
+      <c r="A32" s="3">
         <v>49</v>
       </c>
-      <c r="B32" t="s">
-        <v>17</v>
-      </c>
-      <c r="C32" t="s">
-        <v>283</v>
-      </c>
-      <c r="D32" t="s">
+      <c r="B32" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D32" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E32" t="s">
+      <c r="E32" s="3" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33">
+      <c r="A33" s="3">
         <v>51</v>
       </c>
-      <c r="B33" t="s">
-        <v>17</v>
-      </c>
-      <c r="C33" t="s">
-        <v>284</v>
-      </c>
-      <c r="D33" t="s">
+      <c r="B33" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D33" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="E33" s="7" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34">
+      <c r="A34" s="3">
         <v>53</v>
       </c>
-      <c r="B34" t="s">
-        <v>17</v>
-      </c>
-      <c r="C34" t="s">
-        <v>284</v>
-      </c>
-      <c r="D34" t="s">
+      <c r="B34" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D34" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E34" t="s">
+      <c r="E34" s="3" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35">
+      <c r="A35" s="3">
         <v>55</v>
       </c>
-      <c r="B35" t="s">
-        <v>17</v>
-      </c>
-      <c r="C35" t="s">
-        <v>283</v>
-      </c>
-      <c r="D35" t="s">
+      <c r="B35" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D35" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E35" t="s">
+      <c r="E35" s="3" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36">
+      <c r="A36" s="3">
         <v>57</v>
       </c>
-      <c r="B36" t="s">
-        <v>17</v>
-      </c>
-      <c r="C36" t="s">
-        <v>283</v>
-      </c>
-      <c r="D36" t="s">
+      <c r="B36" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D36" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E36" t="s">
+      <c r="E36" s="3" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A37">
+      <c r="A37" s="3">
         <v>59</v>
       </c>
-      <c r="B37" t="s">
-        <v>17</v>
-      </c>
-      <c r="C37" t="s">
-        <v>283</v>
-      </c>
-      <c r="D37" t="s">
+      <c r="B37" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D37" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="E37" t="s">
+      <c r="E37" s="3" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A38">
+      <c r="A38" s="3">
         <v>61</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="C38" t="s">
-        <v>283</v>
-      </c>
-      <c r="D38" t="s">
+      <c r="C38" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D38" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E38" t="s">
+      <c r="E38" s="3" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A39">
+      <c r="A39" s="3">
         <v>63</v>
       </c>
-      <c r="B39" t="s">
-        <v>17</v>
-      </c>
-      <c r="C39" t="s">
-        <v>283</v>
-      </c>
-      <c r="D39" t="s">
+      <c r="B39" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D39" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="E39" t="s">
+      <c r="E39" s="3" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A40">
+      <c r="A40" s="3">
         <v>65</v>
       </c>
-      <c r="B40" t="s">
-        <v>17</v>
-      </c>
-      <c r="C40" t="s">
-        <v>283</v>
-      </c>
-      <c r="D40" t="s">
+      <c r="B40" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D40" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="E40" t="s">
+      <c r="E40" s="3" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A41">
+      <c r="A41" s="3">
         <v>67</v>
       </c>
-      <c r="B41" t="s">
-        <v>17</v>
-      </c>
-      <c r="C41" t="s">
-        <v>283</v>
-      </c>
-      <c r="D41" t="s">
+      <c r="B41" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D41" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="E41" t="s">
+      <c r="E41" s="3" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A42">
+      <c r="A42" s="3">
         <v>69</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="C42" t="s">
-        <v>283</v>
-      </c>
-      <c r="D42" t="s">
+      <c r="C42" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D42" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E42" t="s">
+      <c r="E42" s="3" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A43">
+      <c r="A43" s="3">
         <v>71</v>
       </c>
-      <c r="B43" t="s">
-        <v>17</v>
-      </c>
-      <c r="C43" t="s">
-        <v>283</v>
-      </c>
-      <c r="D43" t="s">
+      <c r="B43" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D43" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E43" t="s">
+      <c r="E43" s="3" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A44">
+      <c r="A44" s="3">
         <v>73</v>
       </c>
-      <c r="B44" t="s">
-        <v>17</v>
-      </c>
-      <c r="C44" t="s">
-        <v>283</v>
-      </c>
-      <c r="D44" t="s">
+      <c r="B44" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D44" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="E44" t="s">
+      <c r="E44" s="3" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A45">
+      <c r="A45" s="3">
         <v>75</v>
       </c>
-      <c r="B45" t="s">
-        <v>17</v>
-      </c>
-      <c r="C45" t="s">
-        <v>283</v>
-      </c>
-      <c r="D45" t="s">
+      <c r="B45" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D45" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E45" t="s">
+      <c r="E45" s="3" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A46">
+      <c r="A46" s="3">
         <v>77</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="C46" t="s">
-        <v>283</v>
-      </c>
-      <c r="D46" t="s">
+      <c r="C46" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D46" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="E46" t="s">
+      <c r="E46" s="3" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A47">
+      <c r="A47" s="3">
         <v>79</v>
       </c>
-      <c r="B47" t="s">
-        <v>17</v>
-      </c>
-      <c r="C47" t="s">
-        <v>283</v>
-      </c>
-      <c r="D47" t="s">
+      <c r="B47" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D47" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="E47" t="s">
+      <c r="E47" s="3" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A48">
+      <c r="A48" s="3">
         <v>81</v>
       </c>
-      <c r="B48" t="s">
-        <v>17</v>
-      </c>
-      <c r="C48" t="s">
-        <v>283</v>
-      </c>
-      <c r="D48" t="s">
+      <c r="B48" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D48" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E48" t="s">
+      <c r="E48" s="3" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A49">
+      <c r="A49" s="3">
         <v>83</v>
       </c>
-      <c r="B49" t="s">
-        <v>17</v>
-      </c>
-      <c r="C49" t="s">
-        <v>283</v>
-      </c>
-      <c r="D49" t="s">
+      <c r="B49" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D49" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="E49" t="s">
+      <c r="E49" s="3" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A50">
+      <c r="A50" s="3">
         <v>85</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="C50" t="s">
-        <v>283</v>
-      </c>
-      <c r="D50" t="s">
+      <c r="C50" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D50" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="E50" t="s">
+      <c r="E50" s="3" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A51">
+      <c r="A51" s="3">
         <v>87</v>
       </c>
-      <c r="B51" t="s">
-        <v>17</v>
-      </c>
-      <c r="C51" t="s">
-        <v>283</v>
-      </c>
-      <c r="D51" t="s">
+      <c r="B51" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D51" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="E51" t="s">
+      <c r="E51" s="3" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A52">
+      <c r="A52" s="3">
         <v>89</v>
       </c>
-      <c r="B52" t="s">
-        <v>17</v>
-      </c>
-      <c r="C52" t="s">
-        <v>283</v>
-      </c>
-      <c r="D52" t="s">
+      <c r="B52" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D52" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="E52" t="s">
+      <c r="E52" s="3" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A53">
+      <c r="A53" s="3">
         <v>91</v>
       </c>
-      <c r="B53" t="s">
-        <v>17</v>
-      </c>
-      <c r="C53" t="s">
-        <v>283</v>
-      </c>
-      <c r="D53" t="s">
+      <c r="B53" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D53" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="E53" t="s">
+      <c r="E53" s="3" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A54">
+      <c r="A54" s="3">
         <v>93</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="C54" t="s">
-        <v>283</v>
-      </c>
-      <c r="D54" t="s">
+      <c r="C54" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D54" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="E54" t="s">
+      <c r="E54" s="3" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A55">
+      <c r="A55" s="3">
         <v>103</v>
       </c>
-      <c r="B55" t="s">
-        <v>17</v>
-      </c>
-      <c r="C55" t="s">
-        <v>284</v>
-      </c>
-      <c r="D55" t="s">
+      <c r="B55" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D55" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="E55" s="1" t="s">
+      <c r="E55" s="7" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A56">
+      <c r="A56" s="3">
         <v>105</v>
       </c>
-      <c r="B56" t="s">
-        <v>17</v>
-      </c>
-      <c r="C56" t="s">
-        <v>284</v>
-      </c>
-      <c r="D56" t="s">
+      <c r="B56" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D56" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E56" s="1" t="s">
+      <c r="E56" s="7" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A57">
+      <c r="A57" s="3">
         <v>107</v>
       </c>
-      <c r="B57" t="s">
-        <v>17</v>
-      </c>
-      <c r="C57" t="s">
-        <v>284</v>
-      </c>
-      <c r="D57" t="s">
+      <c r="B57" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D57" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E57" s="1" t="s">
+      <c r="E57" s="7" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A58">
+      <c r="A58" s="3">
         <v>109</v>
       </c>
-      <c r="B58" t="s">
-        <v>17</v>
-      </c>
-      <c r="C58" t="s">
-        <v>284</v>
-      </c>
-      <c r="D58" t="s">
+      <c r="B58" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D58" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="E58" s="1" t="s">
+      <c r="E58" s="7" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A59">
+      <c r="A59" s="3">
         <v>111</v>
       </c>
-      <c r="B59" t="s">
-        <v>17</v>
-      </c>
-      <c r="C59" t="s">
-        <v>284</v>
-      </c>
-      <c r="D59" t="s">
+      <c r="B59" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D59" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E59" s="1" t="s">
+      <c r="E59" s="7" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A60">
+      <c r="A60" s="3">
         <v>115</v>
       </c>
-      <c r="B60" t="s">
-        <v>17</v>
-      </c>
-      <c r="C60" t="s">
-        <v>283</v>
-      </c>
-      <c r="D60" t="s">
+      <c r="B60" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D60" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="E60" t="s">
+      <c r="E60" s="3" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A61">
+      <c r="A61" s="3">
         <v>117</v>
       </c>
-      <c r="B61" t="s">
-        <v>17</v>
-      </c>
-      <c r="C61" t="s">
-        <v>283</v>
-      </c>
-      <c r="D61" t="s">
+      <c r="B61" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D61" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E61" t="s">
+      <c r="E61" s="3" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A62">
+      <c r="A62" s="3">
         <v>119</v>
       </c>
-      <c r="B62" t="s">
-        <v>17</v>
-      </c>
-      <c r="C62" t="s">
-        <v>283</v>
-      </c>
-      <c r="D62" t="s">
+      <c r="B62" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D62" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="E62" t="s">
+      <c r="E62" s="3" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A63">
+      <c r="A63" s="3">
         <v>121</v>
       </c>
-      <c r="B63" t="s">
-        <v>17</v>
-      </c>
-      <c r="C63" t="s">
-        <v>283</v>
-      </c>
-      <c r="D63" t="s">
+      <c r="B63" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D63" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="E63" t="s">
+      <c r="E63" s="3" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A64">
+      <c r="A64" s="3">
         <v>123</v>
       </c>
-      <c r="B64" t="s">
-        <v>17</v>
-      </c>
-      <c r="C64" t="s">
-        <v>283</v>
-      </c>
-      <c r="D64" t="s">
+      <c r="B64" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D64" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="E64" t="s">
+      <c r="E64" s="3" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A65">
+      <c r="A65" s="3">
         <v>125</v>
       </c>
-      <c r="B65" t="s">
-        <v>17</v>
-      </c>
-      <c r="C65" t="s">
-        <v>283</v>
-      </c>
-      <c r="D65" t="s">
+      <c r="B65" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D65" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="E65" t="s">
+      <c r="E65" s="3" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A66">
+      <c r="A66" s="3">
         <v>127</v>
       </c>
-      <c r="B66" t="s">
-        <v>17</v>
-      </c>
-      <c r="C66" t="s">
-        <v>283</v>
-      </c>
-      <c r="D66" t="s">
+      <c r="B66" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D66" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="E66" t="s">
+      <c r="E66" s="3" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A67">
+      <c r="A67" s="3">
         <v>129</v>
       </c>
-      <c r="B67" t="s">
-        <v>17</v>
-      </c>
-      <c r="C67" t="s">
-        <v>283</v>
-      </c>
-      <c r="D67" t="s">
+      <c r="B67" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D67" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="E67" t="s">
+      <c r="E67" s="3" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A68">
+      <c r="A68" s="3">
         <v>131</v>
       </c>
-      <c r="B68" t="s">
-        <v>17</v>
-      </c>
-      <c r="C68" t="s">
-        <v>283</v>
-      </c>
-      <c r="D68" t="s">
+      <c r="B68" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D68" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="E68" t="s">
+      <c r="E68" s="3" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A69">
+      <c r="A69" s="3">
         <v>133</v>
       </c>
-      <c r="B69" t="s">
-        <v>17</v>
-      </c>
-      <c r="C69" t="s">
-        <v>283</v>
-      </c>
-      <c r="D69" t="s">
+      <c r="B69" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D69" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="E69" t="s">
+      <c r="E69" s="3" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A70">
+      <c r="A70" s="3">
         <v>135</v>
       </c>
-      <c r="B70" t="s">
-        <v>17</v>
-      </c>
-      <c r="C70" t="s">
-        <v>283</v>
-      </c>
-      <c r="D70" t="s">
+      <c r="B70" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D70" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="E70" t="s">
+      <c r="E70" s="3" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A71">
+      <c r="A71" s="3">
         <v>157</v>
       </c>
-      <c r="B71" t="s">
-        <v>17</v>
-      </c>
-      <c r="C71" t="s">
-        <v>284</v>
-      </c>
-      <c r="D71" t="s">
+      <c r="B71" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D71" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="E71" t="s">
+      <c r="E71" s="3" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A72">
+      <c r="A72" s="3">
         <v>159</v>
       </c>
-      <c r="B72" t="s">
-        <v>17</v>
-      </c>
-      <c r="C72" t="s">
-        <v>284</v>
-      </c>
-      <c r="D72" t="s">
+      <c r="B72" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D72" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="E72" t="s">
+      <c r="E72" s="3" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A73">
+      <c r="A73" s="3">
         <v>161</v>
       </c>
-      <c r="B73" t="s">
-        <v>17</v>
-      </c>
-      <c r="C73" t="s">
-        <v>283</v>
-      </c>
-      <c r="D73" t="s">
+      <c r="B73" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D73" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E73" t="s">
+      <c r="E73" s="3" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A74">
+      <c r="A74" s="3">
         <v>163</v>
       </c>
-      <c r="B74" t="s">
-        <v>17</v>
-      </c>
-      <c r="C74" t="s">
-        <v>283</v>
-      </c>
-      <c r="D74" t="s">
+      <c r="B74" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D74" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E74" t="s">
+      <c r="E74" s="3" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A75">
+      <c r="A75" s="3">
         <v>165</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B75" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C75" t="s">
-        <v>283</v>
-      </c>
-      <c r="D75" t="s">
+      <c r="C75" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D75" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="E75" t="s">
+      <c r="E75" s="3" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
+      <c r="A76" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B76" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C76" t="s">
-        <v>283</v>
-      </c>
-      <c r="D76" t="s">
+      <c r="C76" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D76" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="E76" t="s">
+      <c r="E76" s="3" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A77">
+      <c r="A77" s="3">
         <v>167</v>
       </c>
-      <c r="B77" t="s">
-        <v>17</v>
-      </c>
-      <c r="C77" t="s">
-        <v>283</v>
-      </c>
-      <c r="D77" t="s">
+      <c r="B77" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D77" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E77" t="s">
+      <c r="E77" s="3" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A78">
+      <c r="A78" s="3">
         <v>169</v>
       </c>
-      <c r="B78" t="s">
-        <v>17</v>
-      </c>
-      <c r="C78" t="s">
-        <v>283</v>
-      </c>
-      <c r="D78" t="s">
+      <c r="B78" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D78" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="E78" t="s">
+      <c r="E78" s="3" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A79">
+      <c r="A79" s="3">
         <v>171</v>
       </c>
-      <c r="B79" t="s">
-        <v>17</v>
-      </c>
-      <c r="C79" t="s">
-        <v>283</v>
-      </c>
-      <c r="D79" t="s">
+      <c r="B79" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D79" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="E79" t="s">
+      <c r="E79" s="3" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A80">
+      <c r="A80" s="3">
         <v>173</v>
       </c>
-      <c r="B80" t="s">
-        <v>17</v>
-      </c>
-      <c r="C80" t="s">
-        <v>283</v>
-      </c>
-      <c r="D80" t="s">
+      <c r="B80" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D80" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="E80" t="s">
+      <c r="E80" s="3" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A81">
+      <c r="A81" s="3">
         <v>175</v>
       </c>
-      <c r="B81" t="s">
-        <v>17</v>
-      </c>
-      <c r="C81" t="s">
-        <v>283</v>
-      </c>
-      <c r="D81" t="s">
+      <c r="B81" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D81" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="E81" t="s">
+      <c r="E81" s="3" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A82">
+      <c r="A82" s="3">
         <v>177</v>
       </c>
-      <c r="B82" t="s">
-        <v>17</v>
-      </c>
-      <c r="C82" t="s">
-        <v>283</v>
-      </c>
-      <c r="D82" t="s">
+      <c r="B82" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D82" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="E82" t="s">
+      <c r="E82" s="3" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A83">
+      <c r="A83" s="3">
         <v>179</v>
       </c>
-      <c r="B83" t="s">
-        <v>17</v>
-      </c>
-      <c r="C83" t="s">
-        <v>283</v>
-      </c>
-      <c r="D83" t="s">
+      <c r="B83" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D83" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="E83" t="s">
+      <c r="E83" s="3" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A84">
+      <c r="A84" s="3">
         <v>181</v>
       </c>
-      <c r="B84" t="s">
-        <v>17</v>
-      </c>
-      <c r="C84" t="s">
-        <v>284</v>
-      </c>
-      <c r="D84" t="s">
+      <c r="B84" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D84" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="E84" s="1" t="s">
+      <c r="E84" s="7" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A85">
+      <c r="A85" s="3">
         <v>183</v>
       </c>
-      <c r="B85" t="s">
-        <v>17</v>
-      </c>
-      <c r="C85" t="s">
-        <v>284</v>
-      </c>
-      <c r="D85" t="s">
+      <c r="B85" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D85" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="E85" t="s">
+      <c r="E85" s="3" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A86">
+      <c r="A86" s="3">
         <v>185</v>
       </c>
-      <c r="B86" t="s">
-        <v>17</v>
-      </c>
-      <c r="C86" t="s">
-        <v>284</v>
-      </c>
-      <c r="D86" t="s">
+      <c r="B86" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D86" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="E86" t="s">
+      <c r="E86" s="3" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A87">
+      <c r="A87" s="3">
         <v>187</v>
       </c>
-      <c r="B87" t="s">
-        <v>17</v>
-      </c>
-      <c r="C87" t="s">
-        <v>283</v>
-      </c>
-      <c r="D87" t="s">
+      <c r="B87" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D87" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="E87" t="s">
+      <c r="E87" s="3" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A88">
+      <c r="A88" s="3">
         <v>189</v>
       </c>
-      <c r="B88" t="s">
-        <v>17</v>
-      </c>
-      <c r="C88" t="s">
-        <v>283</v>
-      </c>
-      <c r="D88" t="s">
+      <c r="B88" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D88" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="E88" t="s">
+      <c r="E88" s="3" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A89">
+      <c r="A89" s="3">
         <v>191</v>
       </c>
-      <c r="B89" t="s">
-        <v>17</v>
-      </c>
-      <c r="C89" t="s">
-        <v>283</v>
-      </c>
-      <c r="D89" t="s">
+      <c r="B89" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D89" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="E89" t="s">
+      <c r="E89" s="3" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A90">
+      <c r="A90" s="3">
         <v>193</v>
       </c>
-      <c r="B90" t="s">
-        <v>17</v>
-      </c>
-      <c r="C90" t="s">
-        <v>283</v>
-      </c>
-      <c r="D90" t="s">
+      <c r="B90" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D90" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="E90" t="s">
+      <c r="E90" s="3" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A91">
+      <c r="A91" s="3">
         <v>195</v>
       </c>
-      <c r="B91" t="s">
-        <v>17</v>
-      </c>
-      <c r="C91" t="s">
-        <v>283</v>
-      </c>
-      <c r="D91" t="s">
+      <c r="B91" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D91" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="E91" t="s">
+      <c r="E91" s="3" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A92">
+      <c r="A92" s="3">
         <v>197</v>
       </c>
-      <c r="B92" t="s">
-        <v>17</v>
-      </c>
-      <c r="C92" t="s">
-        <v>283</v>
-      </c>
-      <c r="D92" t="s">
+      <c r="B92" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D92" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="E92" t="s">
+      <c r="E92" s="3" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A93">
+      <c r="A93" s="3">
         <v>199</v>
       </c>
-      <c r="B93" t="s">
-        <v>17</v>
-      </c>
-      <c r="C93" t="s">
-        <v>283</v>
-      </c>
-      <c r="D93" t="s">
+      <c r="B93" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D93" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="E93" t="s">
+      <c r="E93" s="3" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A94">
+      <c r="A94" s="3">
         <v>201</v>
       </c>
-      <c r="B94" t="s">
-        <v>17</v>
-      </c>
-      <c r="C94" t="s">
-        <v>284</v>
-      </c>
-      <c r="D94" t="s">
+      <c r="B94" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D94" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="E94" s="1" t="s">
+      <c r="E94" s="7" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A95">
+      <c r="A95" s="3">
         <v>203</v>
       </c>
-      <c r="B95" t="s">
-        <v>17</v>
-      </c>
-      <c r="C95" t="s">
-        <v>284</v>
-      </c>
-      <c r="D95" t="s">
+      <c r="B95" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D95" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="E95" t="s">
+      <c r="E95" s="3" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A96">
+      <c r="A96" s="3">
         <v>205</v>
       </c>
-      <c r="B96" t="s">
-        <v>17</v>
-      </c>
-      <c r="C96" t="s">
-        <v>284</v>
-      </c>
-      <c r="D96" t="s">
+      <c r="B96" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D96" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="E96" t="s">
+      <c r="E96" s="3" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A97" t="s">
+      <c r="A97" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B97" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C97" t="s">
-        <v>283</v>
-      </c>
-      <c r="D97" t="s">
+      <c r="C97" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D97" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="E97" t="s">
+      <c r="E97" s="3" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A98" s="11" t="s">
+      <c r="A98" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="B98" s="11" t="s">
+      <c r="B98" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C98" s="11" t="s">
-        <v>283</v>
-      </c>
-      <c r="D98" s="11" t="s">
+      <c r="C98" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D98" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="E98" s="11" t="s">
+      <c r="E98" s="3" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A99" s="11" t="s">
+      <c r="A99" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="B99" s="11" t="s">
+      <c r="B99" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C99" s="11" t="s">
-        <v>283</v>
-      </c>
-      <c r="D99" s="11" t="s">
+      <c r="C99" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D99" s="3" t="s">
         <v>454</v>
       </c>
-      <c r="E99" s="11" t="s">
+      <c r="E99" s="3" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="100" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A100" t="s">
+    <row r="100" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="B100" t="s">
+      <c r="B100" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C100" t="s">
-        <v>283</v>
-      </c>
-      <c r="D100" s="3" t="s">
+      <c r="C100" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D100" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E100" s="3" t="s">
+      <c r="E100" s="9" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A101" t="s">
+      <c r="A101" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B101" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C101" t="s">
-        <v>283</v>
-      </c>
-      <c r="D101" t="s">
+      <c r="C101" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D101" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="E101" t="s">
+      <c r="E101" s="3" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="102" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A102" t="s">
+    <row r="102" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B102" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C102" t="s">
-        <v>283</v>
-      </c>
-      <c r="D102" s="3" t="s">
+      <c r="C102" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D102" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="E102" s="3" t="s">
+      <c r="E102" s="9" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="103" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A103" t="s">
+    <row r="103" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B103" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C103" t="s">
-        <v>283</v>
-      </c>
-      <c r="D103" s="3" t="s">
+      <c r="C103" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D103" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="E103" s="3" t="s">
+      <c r="E103" s="9" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A104" t="s">
+      <c r="A104" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B104" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C104" t="s">
-        <v>283</v>
-      </c>
-      <c r="D104" t="s">
+      <c r="C104" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D104" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="E104" t="s">
+      <c r="E104" s="3" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A105" t="s">
+      <c r="A105" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="B105" t="s">
+      <c r="B105" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C105" t="s">
-        <v>283</v>
-      </c>
-      <c r="D105" t="s">
+      <c r="C105" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D105" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="E105" t="s">
+      <c r="E105" s="3" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A106" t="s">
+      <c r="A106" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="B106" t="s">
+      <c r="B106" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C106" t="s">
-        <v>283</v>
-      </c>
-      <c r="D106" t="s">
+      <c r="C106" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D106" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E106" t="s">
+      <c r="E106" s="3" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A107" t="s">
+      <c r="A107" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="B107" t="s">
+      <c r="B107" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C107" t="s">
-        <v>283</v>
-      </c>
-      <c r="D107" t="s">
+      <c r="C107" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D107" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="E107" t="s">
+      <c r="E107" s="3" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A108" t="s">
+      <c r="A108" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="B108" t="s">
+      <c r="B108" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C108" t="s">
-        <v>283</v>
-      </c>
-      <c r="D108" t="s">
+      <c r="C108" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D108" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="E108" t="s">
+      <c r="E108" s="3" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A109" t="s">
+      <c r="A109" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="B109" t="s">
+      <c r="B109" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C109" t="s">
-        <v>283</v>
-      </c>
-      <c r="D109" t="s">
+      <c r="C109" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D109" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="E109" t="s">
+      <c r="E109" s="3" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A110" t="s">
+      <c r="A110" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="B110" t="s">
+      <c r="B110" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C110" t="s">
-        <v>283</v>
-      </c>
-      <c r="D110" t="s">
+      <c r="C110" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D110" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="E110" t="s">
+      <c r="E110" s="3" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A111" t="s">
+      <c r="A111" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="B111" t="s">
+      <c r="B111" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C111" t="s">
-        <v>283</v>
-      </c>
-      <c r="D111" t="s">
+      <c r="C111" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D111" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="E111" t="s">
+      <c r="E111" s="3" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A112" s="13" t="s">
+      <c r="A112" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="B112" s="13" t="s">
+      <c r="B112" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C112" s="13" t="s">
-        <v>283</v>
-      </c>
-      <c r="D112" s="13" t="s">
+      <c r="C112" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D112" s="3" t="s">
         <v>458</v>
       </c>
-      <c r="E112" s="13" t="s">
+      <c r="E112" s="3" t="s">
         <v>459</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A113" s="12" t="s">
+      <c r="A113" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="B113" s="12" t="s">
+      <c r="B113" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C113" s="12" t="s">
-        <v>284</v>
-      </c>
-      <c r="D113" s="12" t="s">
+      <c r="C113" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D113" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="E113" s="12" t="s">
+      <c r="E113" s="3" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A114" s="12" t="s">
+      <c r="A114" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="B114" s="12" t="s">
+      <c r="B114" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C114" s="12" t="s">
-        <v>284</v>
-      </c>
-      <c r="D114" s="12" t="s">
+      <c r="C114" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D114" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="E114" s="12" t="s">
+      <c r="E114" s="3" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A115" s="12" t="s">
+      <c r="A115" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="B115" s="12" t="s">
+      <c r="B115" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C115" s="12" t="s">
-        <v>284</v>
-      </c>
-      <c r="D115" s="12" t="s">
+      <c r="C115" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D115" s="3" t="s">
         <v>456</v>
       </c>
-      <c r="E115" s="12" t="s">
+      <c r="E115" s="3" t="s">
         <v>457</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A116" s="12" t="s">
+      <c r="A116" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="B116" s="12" t="s">
+      <c r="B116" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C116" s="12" t="s">
-        <v>284</v>
-      </c>
-      <c r="D116" s="12" t="s">
+      <c r="C116" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D116" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="E116" s="12" t="s">
+      <c r="E116" s="3" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A117" s="12" t="s">
+      <c r="A117" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="B117" s="12" t="s">
+      <c r="B117" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C117" s="12" t="s">
-        <v>284</v>
-      </c>
-      <c r="D117" s="12" t="s">
+      <c r="C117" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D117" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="E117" s="12" t="s">
+      <c r="E117" s="3" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A118" s="12" t="s">
+      <c r="A118" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="B118" s="12" t="s">
+      <c r="B118" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C118" s="12" t="s">
-        <v>284</v>
-      </c>
-      <c r="D118" s="12" t="s">
+      <c r="C118" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D118" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="E118" s="12" t="s">
+      <c r="E118" s="3" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A119" s="12" t="s">
+      <c r="A119" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="B119" s="12" t="s">
+      <c r="B119" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C119" s="12" t="s">
-        <v>284</v>
-      </c>
-      <c r="D119" s="12" t="s">
+      <c r="C119" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D119" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="E119" s="12" t="s">
+      <c r="E119" s="3" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A120" s="12" t="s">
+      <c r="A120" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="B120" s="12" t="s">
+      <c r="B120" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C120" s="12" t="s">
-        <v>284</v>
-      </c>
-      <c r="D120" s="12" t="s">
+      <c r="C120" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D120" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="E120" s="12" t="s">
+      <c r="E120" s="3" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A121" s="12" t="s">
+      <c r="A121" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="B121" s="12" t="s">
+      <c r="B121" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C121" s="12" t="s">
-        <v>284</v>
-      </c>
-      <c r="D121" s="12" t="s">
+      <c r="C121" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D121" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="E121" s="12" t="s">
+      <c r="E121" s="3" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A122" s="12" t="s">
+      <c r="A122" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="B122" s="12" t="s">
+      <c r="B122" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C122" s="12" t="s">
-        <v>284</v>
-      </c>
-      <c r="D122" s="12" t="s">
+      <c r="C122" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D122" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="E122" s="12" t="s">
+      <c r="E122" s="3" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A123" s="12" t="s">
+      <c r="A123" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="B123" s="12" t="s">
+      <c r="B123" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C123" s="12" t="s">
-        <v>284</v>
-      </c>
-      <c r="D123" s="12" t="s">
+      <c r="C123" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D123" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="E123" s="12" t="s">
+      <c r="E123" s="3" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A124" s="12" t="s">
+      <c r="A124" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="B124" s="12" t="s">
+      <c r="B124" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C124" s="12" t="s">
-        <v>284</v>
-      </c>
-      <c r="D124" s="12" t="s">
+      <c r="C124" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D124" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="E124" s="12" t="s">
+      <c r="E124" s="3" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A125" s="12" t="s">
+      <c r="A125" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="B125" s="12" t="s">
+      <c r="B125" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C125" s="12" t="s">
-        <v>284</v>
-      </c>
-      <c r="D125" s="12" t="s">
+      <c r="C125" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D125" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="E125" s="12" t="s">
+      <c r="E125" s="3" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A126" s="12" t="s">
+      <c r="A126" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="B126" s="12" t="s">
+      <c r="B126" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C126" s="12" t="s">
-        <v>284</v>
-      </c>
-      <c r="D126" s="12" t="s">
+      <c r="C126" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D126" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="E126" s="12" t="s">
+      <c r="E126" s="3" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A127" s="12" t="s">
+      <c r="A127" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="B127" s="12" t="s">
+      <c r="B127" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C127" s="12" t="s">
-        <v>284</v>
-      </c>
-      <c r="D127" s="12" t="s">
+      <c r="C127" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D127" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="E127" s="12" t="s">
+      <c r="E127" s="3" t="s">
         <v>355</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A128" s="12" t="s">
+      <c r="A128" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="B128" s="12" t="s">
+      <c r="B128" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C128" s="12" t="s">
-        <v>284</v>
-      </c>
-      <c r="D128" s="12" t="s">
+      <c r="C128" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D128" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="E128" s="12" t="s">
+      <c r="E128" s="3" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A129">
+      <c r="A129" s="3">
         <v>209</v>
       </c>
-      <c r="B129" t="s">
-        <v>17</v>
-      </c>
-      <c r="C129" t="s">
-        <v>283</v>
-      </c>
-      <c r="D129" t="s">
+      <c r="B129" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C129" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D129" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="E129" t="s">
+      <c r="E129" s="3" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A130">
+      <c r="A130" s="3">
         <v>211</v>
       </c>
-      <c r="B130" t="s">
-        <v>17</v>
-      </c>
-      <c r="C130" t="s">
-        <v>283</v>
-      </c>
-      <c r="D130" t="s">
+      <c r="B130" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C130" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D130" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="E130" t="s">
+      <c r="E130" s="3" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A131">
+      <c r="A131" s="3">
         <v>213</v>
       </c>
-      <c r="B131" t="s">
+      <c r="B131" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="C131" t="s">
-        <v>283</v>
-      </c>
-      <c r="D131" t="s">
+      <c r="C131" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D131" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="E131" t="s">
+      <c r="E131" s="3" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A132" t="s">
+      <c r="A132" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="B132" t="s">
+      <c r="B132" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C132" t="s">
-        <v>284</v>
-      </c>
-      <c r="D132" t="s">
+      <c r="C132" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D132" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="E132" t="s">
+      <c r="E132" s="3" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A133">
+      <c r="A133" s="3">
         <v>224</v>
       </c>
-      <c r="B133" t="s">
-        <v>17</v>
-      </c>
-      <c r="C133" t="s">
-        <v>284</v>
-      </c>
-      <c r="D133" t="s">
+      <c r="B133" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C133" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D133" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="E133" t="s">
+      <c r="E133" s="3" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A134" t="s">
+      <c r="A134" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="B134" t="s">
+      <c r="B134" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C134" t="s">
-        <v>284</v>
-      </c>
-      <c r="D134" t="s">
+      <c r="C134" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D134" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="E134" t="s">
+      <c r="E134" s="3" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A135" t="s">
+      <c r="A135" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="B135" t="s">
+      <c r="B135" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C135" t="s">
-        <v>284</v>
-      </c>
-      <c r="D135" t="s">
+      <c r="C135" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D135" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="E135" t="s">
+      <c r="E135" s="3" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A136" t="s">
+      <c r="A136" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="B136" t="s">
+      <c r="B136" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C136" t="s">
-        <v>284</v>
-      </c>
-      <c r="D136" t="s">
+      <c r="C136" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D136" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="E136" t="s">
+      <c r="E136" s="3" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A137" t="s">
+      <c r="A137" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="B137" t="s">
+      <c r="B137" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C137" t="s">
-        <v>284</v>
-      </c>
-      <c r="D137" t="s">
+      <c r="C137" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D137" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="E137" t="s">
+      <c r="E137" s="3" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A138" t="s">
+      <c r="A138" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="B138" t="s">
+      <c r="B138" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C138" t="s">
-        <v>284</v>
-      </c>
-      <c r="D138" t="s">
+      <c r="C138" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D138" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="E138" t="s">
+      <c r="E138" s="3" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A139" t="s">
+      <c r="A139" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="B139" t="s">
+      <c r="B139" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C139" t="s">
-        <v>284</v>
-      </c>
-      <c r="D139" t="s">
+      <c r="C139" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D139" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="E139" t="s">
+      <c r="E139" s="3" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A140" t="s">
+      <c r="A140" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="B140" t="s">
+      <c r="B140" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C140" t="s">
-        <v>284</v>
-      </c>
-      <c r="D140" t="s">
+      <c r="C140" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D140" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="E140" t="s">
+      <c r="E140" s="3" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A141" t="s">
+      <c r="A141" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="B141" t="s">
+      <c r="B141" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C141" t="s">
-        <v>284</v>
-      </c>
-      <c r="D141" t="s">
+      <c r="C141" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D141" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="E141" t="s">
+      <c r="E141" s="3" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A142" s="5" t="s">
+      <c r="A142" s="10" t="s">
         <v>362</v>
       </c>
-      <c r="B142" s="5" t="s">
+      <c r="B142" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="C142" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="D142" s="5" t="s">
+      <c r="C142" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="D142" s="10" t="s">
         <v>360</v>
       </c>
-      <c r="E142" s="5" t="s">
+      <c r="E142" s="10" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A143" s="5" t="s">
+      <c r="A143" s="10" t="s">
         <v>364</v>
       </c>
-      <c r="B143" s="5" t="s">
+      <c r="B143" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="C143" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="D143" s="5" t="s">
+      <c r="C143" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="D143" s="10" t="s">
         <v>361</v>
       </c>
-      <c r="E143" s="5" t="s">
+      <c r="E143" s="10" t="s">
         <v>363</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A144">
+      <c r="A144" s="3">
         <v>239</v>
       </c>
-      <c r="B144" t="s">
-        <v>17</v>
-      </c>
-      <c r="C144" t="s">
-        <v>284</v>
-      </c>
-      <c r="D144" t="s">
+      <c r="B144" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C144" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D144" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="E144" t="s">
+      <c r="E144" s="3" t="s">
         <v>410</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A145">
+      <c r="A145" s="3">
         <v>245</v>
       </c>
-      <c r="B145" t="s">
-        <v>17</v>
-      </c>
-      <c r="C145" t="s">
-        <v>284</v>
-      </c>
-      <c r="D145" t="s">
+      <c r="B145" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C145" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D145" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="E145" t="s">
+      <c r="E145" s="3" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A146">
+      <c r="A146" s="3">
         <v>247</v>
       </c>
-      <c r="B146" t="s">
-        <v>17</v>
-      </c>
-      <c r="C146" t="s">
-        <v>283</v>
-      </c>
-      <c r="D146" t="s">
+      <c r="B146" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C146" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D146" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="E146" t="s">
+      <c r="E146" s="3" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A147">
+      <c r="A147" s="3">
         <v>249</v>
       </c>
-      <c r="B147" t="s">
-        <v>17</v>
-      </c>
-      <c r="C147" t="s">
-        <v>283</v>
-      </c>
-      <c r="D147" t="s">
+      <c r="B147" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C147" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D147" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="E147" t="s">
+      <c r="E147" s="3" t="s">
         <v>319</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A148">
+      <c r="A148" s="3">
         <v>251</v>
       </c>
-      <c r="B148" t="s">
-        <v>17</v>
-      </c>
-      <c r="C148" t="s">
-        <v>283</v>
-      </c>
-      <c r="D148" t="s">
+      <c r="B148" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C148" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D148" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="E148" t="s">
+      <c r="E148" s="3" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A149">
+      <c r="A149" s="3">
         <v>253</v>
       </c>
-      <c r="B149" t="s">
-        <v>17</v>
-      </c>
-      <c r="C149" t="s">
-        <v>283</v>
-      </c>
-      <c r="D149" t="s">
+      <c r="B149" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C149" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D149" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="E149" t="s">
+      <c r="E149" s="3" t="s">
         <v>320</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A150" s="4">
+      <c r="A150" s="11">
         <v>255</v>
       </c>
-      <c r="B150" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C150" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="D150" s="4" t="s">
+      <c r="B150" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C150" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="D150" s="11" t="s">
         <v>304</v>
       </c>
-      <c r="E150" s="4" t="s">
+      <c r="E150" s="11" t="s">
         <v>330</v>
       </c>
-      <c r="F150" s="8" t="s">
+      <c r="F150" s="4" t="s">
         <v>345</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A151" s="4">
+      <c r="A151" s="11">
         <v>257</v>
       </c>
-      <c r="B151" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C151" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="D151" s="4" t="s">
+      <c r="B151" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C151" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="D151" s="11" t="s">
         <v>305</v>
       </c>
-      <c r="E151" s="4" t="s">
+      <c r="E151" s="11" t="s">
         <v>322</v>
       </c>
-      <c r="F151" s="8"/>
+      <c r="F151" s="4"/>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A152" s="4">
+      <c r="A152" s="11">
         <v>259</v>
       </c>
-      <c r="B152" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C152" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="D152" s="4" t="s">
+      <c r="B152" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C152" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="D152" s="11" t="s">
         <v>306</v>
       </c>
-      <c r="E152" s="4" t="s">
+      <c r="E152" s="11" t="s">
         <v>323</v>
       </c>
-      <c r="F152" s="8"/>
+      <c r="F152" s="4"/>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A153" s="4">
+      <c r="A153" s="11">
         <v>261</v>
       </c>
-      <c r="B153" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C153" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="D153" s="4" t="s">
+      <c r="B153" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C153" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="D153" s="11" t="s">
         <v>307</v>
       </c>
-      <c r="E153" s="4" t="s">
+      <c r="E153" s="11" t="s">
         <v>324</v>
       </c>
-      <c r="F153" s="8"/>
+      <c r="F153" s="4"/>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A154" s="4">
+      <c r="A154" s="11">
         <v>263</v>
       </c>
-      <c r="B154" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C154" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="D154" s="4" t="s">
+      <c r="B154" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C154" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="D154" s="11" t="s">
         <v>308</v>
       </c>
-      <c r="E154" s="4" t="s">
+      <c r="E154" s="11" t="s">
         <v>325</v>
       </c>
-      <c r="F154" s="8"/>
+      <c r="F154" s="4"/>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A155" s="4">
+      <c r="A155" s="11">
         <v>265</v>
       </c>
-      <c r="B155" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C155" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="D155" s="4" t="s">
+      <c r="B155" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C155" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="D155" s="11" t="s">
         <v>309</v>
       </c>
-      <c r="E155" s="4" t="s">
+      <c r="E155" s="11" t="s">
         <v>321</v>
       </c>
-      <c r="F155" s="8"/>
+      <c r="F155" s="4"/>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A156" s="4">
+      <c r="A156" s="11">
         <v>267</v>
       </c>
-      <c r="B156" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C156" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="D156" s="4" t="s">
+      <c r="B156" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C156" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="D156" s="11" t="s">
         <v>310</v>
       </c>
-      <c r="E156" s="4" t="s">
+      <c r="E156" s="11" t="s">
         <v>326</v>
       </c>
-      <c r="F156" s="8"/>
+      <c r="F156" s="4"/>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A157" s="4">
+      <c r="A157" s="11">
         <v>269</v>
       </c>
-      <c r="B157" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C157" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="D157" s="4" t="s">
+      <c r="B157" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C157" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="D157" s="11" t="s">
         <v>311</v>
       </c>
-      <c r="E157" s="4" t="s">
+      <c r="E157" s="11" t="s">
         <v>327</v>
       </c>
-      <c r="F157" s="8"/>
+      <c r="F157" s="4"/>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A158" s="4">
+      <c r="A158" s="11">
         <v>271</v>
       </c>
-      <c r="B158" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C158" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="D158" s="4" t="s">
+      <c r="B158" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C158" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="D158" s="11" t="s">
         <v>312</v>
       </c>
-      <c r="E158" s="4" t="s">
+      <c r="E158" s="11" t="s">
         <v>328</v>
       </c>
-      <c r="F158" s="8"/>
+      <c r="F158" s="4"/>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A159" s="4">
+      <c r="A159" s="11">
         <v>273</v>
       </c>
-      <c r="B159" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C159" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="D159" s="4" t="s">
+      <c r="B159" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C159" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="D159" s="11" t="s">
         <v>313</v>
       </c>
-      <c r="E159" s="4" t="s">
+      <c r="E159" s="11" t="s">
         <v>329</v>
       </c>
-      <c r="F159" s="8"/>
+      <c r="F159" s="4"/>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A160">
+      <c r="A160" s="3">
         <v>275</v>
       </c>
-      <c r="B160" t="s">
-        <v>17</v>
-      </c>
-      <c r="C160" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="D160" t="s">
+      <c r="B160" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C160" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="D160" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="E160" t="s">
+      <c r="E160" s="3" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A161">
+      <c r="A161" s="3">
         <v>277</v>
       </c>
-      <c r="B161" t="s">
-        <v>17</v>
-      </c>
-      <c r="C161" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="D161" t="s">
+      <c r="B161" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C161" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="D161" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="E161" t="s">
+      <c r="E161" s="3" t="s">
         <v>351</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A162">
+      <c r="A162" s="3">
         <v>279</v>
       </c>
-      <c r="B162" t="s">
+      <c r="B162" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="C162" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="D162" t="s">
+      <c r="C162" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="D162" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="E162" t="s">
+      <c r="E162" s="3" t="s">
         <v>352</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A163" s="6" t="s">
+      <c r="A163" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="B163" s="6" t="s">
+      <c r="B163" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C163" s="6" t="s">
-        <v>283</v>
-      </c>
-      <c r="D163" s="6" t="s">
+      <c r="C163" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="D163" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="E163" s="6" t="s">
+      <c r="E163" s="2" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A164" s="6" t="s">
+      <c r="A164" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="B164" s="6" t="s">
+      <c r="B164" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C164" s="6" t="s">
-        <v>283</v>
-      </c>
-      <c r="D164" s="6" t="s">
+      <c r="C164" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="D164" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="E164" s="6" t="s">
+      <c r="E164" s="2" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A165" s="6">
-        <v>284</v>
-      </c>
-      <c r="B165" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C165" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="D165" s="6" t="s">
+      <c r="A165" s="2">
+        <v>284</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D165" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="E165" s="6" t="s">
+      <c r="E165" s="2" t="s">
         <v>393</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A166" s="6">
+      <c r="A166" s="2">
         <v>286</v>
       </c>
-      <c r="B166" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C166" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="D166" s="6" t="s">
+      <c r="B166" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C166" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D166" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="E166" s="6" t="s">
+      <c r="E166" s="2" t="s">
         <v>394</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A167" s="6" t="s">
+      <c r="A167" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="B167" s="6" t="s">
+      <c r="B167" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C167" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="D167" s="6" t="s">
+      <c r="C167" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D167" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="E167" s="6" t="s">
+      <c r="E167" s="2" t="s">
         <v>396</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A168" s="6" t="s">
+      <c r="A168" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="B168" s="6" t="s">
+      <c r="B168" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C168" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="D168" s="6" t="s">
+      <c r="C168" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D168" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="E168" s="6" t="s">
+      <c r="E168" s="2" t="s">
         <v>395</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A169" s="6" t="s">
+      <c r="A169" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="B169" s="6" t="s">
+      <c r="B169" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C169" s="6" t="s">
-        <v>283</v>
-      </c>
-      <c r="D169" s="6" t="s">
+      <c r="C169" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="D169" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="E169" s="6" t="s">
+      <c r="E169" s="2" t="s">
         <v>397</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A170" s="6">
+      <c r="A170" s="2">
         <v>289</v>
       </c>
-      <c r="B170" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C170" s="6" t="s">
-        <v>283</v>
-      </c>
-      <c r="D170" s="6" t="s">
+      <c r="B170" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C170" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="D170" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="E170" s="6" t="s">
+      <c r="E170" s="2" t="s">
         <v>398</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A171" s="6">
+      <c r="A171" s="2">
         <v>291</v>
       </c>
-      <c r="B171" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C171" s="6" t="s">
-        <v>283</v>
-      </c>
-      <c r="D171" s="6" t="s">
+      <c r="B171" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C171" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="D171" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="E171" s="6" t="s">
+      <c r="E171" s="2" t="s">
         <v>399</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A172" s="6">
+      <c r="A172" s="2">
         <v>293</v>
       </c>
-      <c r="B172" s="6" t="s">
+      <c r="B172" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C172" s="6" t="s">
-        <v>283</v>
-      </c>
-      <c r="D172" s="6" t="s">
+      <c r="C172" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="D172" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="E172" s="6" t="s">
+      <c r="E172" s="2" t="s">
         <v>400</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A173" s="6">
+      <c r="A173" s="2">
         <v>295</v>
       </c>
-      <c r="B173" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C173" s="6" t="s">
-        <v>283</v>
-      </c>
-      <c r="D173" s="6" t="s">
+      <c r="B173" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C173" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="D173" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="E173" s="6" t="s">
+      <c r="E173" s="2" t="s">
         <v>401</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A174" s="6">
+      <c r="A174" s="2">
         <v>297</v>
       </c>
-      <c r="B174" s="6" t="s">
+      <c r="B174" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="C174" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="D174" s="6" t="s">
+      <c r="C174" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D174" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="E174" s="6" t="s">
+      <c r="E174" s="2" t="s">
         <v>402</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A175" s="6">
+      <c r="A175" s="2">
         <v>327</v>
       </c>
-      <c r="B175" s="6" t="s">
+      <c r="B175" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="C175" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="D175" s="6" t="s">
+      <c r="C175" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D175" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="E175" s="6" t="s">
+      <c r="E175" s="2" t="s">
         <v>403</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A176" s="6">
+      <c r="A176" s="2">
         <v>357</v>
       </c>
-      <c r="B176" s="6" t="s">
+      <c r="B176" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="C176" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="D176" s="6" t="s">
+      <c r="C176" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D176" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="E176" s="6" t="s">
+      <c r="E176" s="2" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A177" s="6">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A177" s="2">
         <v>387</v>
       </c>
-      <c r="B177" s="6" t="s">
+      <c r="B177" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="C177" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="D177" s="6" t="s">
+      <c r="C177" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D177" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="E177" s="6" t="s">
+      <c r="E177" s="2" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A178" s="6">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A178" s="2">
         <v>447</v>
       </c>
-      <c r="B178" s="6" t="s">
+      <c r="B178" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="C178" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="D178" s="6" t="s">
+      <c r="C178" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D178" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="E178" s="6" t="s">
+      <c r="E178" s="2" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A179" s="6">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A179" s="2">
         <v>507</v>
       </c>
-      <c r="B179" s="6" t="s">
+      <c r="B179" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="C179" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="D179" s="6" t="s">
+      <c r="C179" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D179" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="E179" s="6" t="s">
+      <c r="E179" s="2" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A180" s="6">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A180" s="12">
         <v>567</v>
       </c>
-      <c r="B180" s="6" t="s">
+      <c r="B180" s="12" t="s">
         <v>383</v>
       </c>
-      <c r="C180" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="D180" s="6" t="s">
+      <c r="C180" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="D180" s="12" t="s">
         <v>386</v>
       </c>
-      <c r="E180" s="6" t="s">
+      <c r="E180" s="12" t="s">
         <v>408</v>
       </c>
-    </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A181" s="7">
+      <c r="F180" s="5"/>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A181" s="12">
         <f>274/2</f>
         <v>137</v>
       </c>
-      <c r="B181" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C181" s="7" t="s">
-        <v>283</v>
-      </c>
-      <c r="D181" s="7" t="s">
+      <c r="B181" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C181" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="D181" s="12" t="s">
         <v>411</v>
       </c>
-      <c r="E181" s="7" t="s">
+      <c r="E181" s="12" t="s">
         <v>417</v>
       </c>
-    </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A182" s="7">
+      <c r="F181" s="5"/>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A182" s="12">
         <v>141</v>
       </c>
-      <c r="B182" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C182" s="7" t="s">
-        <v>284</v>
-      </c>
-      <c r="D182" s="7" t="s">
+      <c r="B182" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C182" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="D182" s="12" t="s">
         <v>412</v>
       </c>
-      <c r="E182" s="7" t="s">
+      <c r="E182" s="12" t="s">
         <v>418</v>
       </c>
-    </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A183" s="7">
+      <c r="F182" s="5"/>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A183" s="12">
         <v>145</v>
       </c>
-      <c r="B183" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C183" s="7" t="s">
-        <v>284</v>
-      </c>
-      <c r="D183" s="7" t="s">
+      <c r="B183" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C183" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="D183" s="12" t="s">
         <v>413</v>
       </c>
-      <c r="E183" s="7" t="s">
+      <c r="E183" s="12" t="s">
         <v>419</v>
       </c>
-    </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A184" s="7">
+      <c r="F183" s="5"/>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A184" s="12">
         <v>147</v>
       </c>
-      <c r="B184" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C184" s="7" t="s">
-        <v>283</v>
-      </c>
-      <c r="D184" s="7" t="s">
+      <c r="B184" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C184" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="D184" s="12" t="s">
         <v>414</v>
       </c>
-      <c r="E184" s="7" t="s">
+      <c r="E184" s="12" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A185" s="7">
+      <c r="F184" s="5"/>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A185" s="12">
         <v>151</v>
       </c>
-      <c r="B185" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C185" s="7" t="s">
-        <v>284</v>
-      </c>
-      <c r="D185" s="7" t="s">
+      <c r="B185" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C185" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="D185" s="12" t="s">
         <v>415</v>
       </c>
-      <c r="E185" s="7" t="s">
+      <c r="E185" s="12" t="s">
         <v>421</v>
       </c>
-    </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A186" s="7">
+      <c r="F185" s="5"/>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A186" s="12">
         <v>155</v>
       </c>
-      <c r="B186" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C186" s="7" t="s">
-        <v>284</v>
-      </c>
-      <c r="D186" s="7" t="s">
+      <c r="B186" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C186" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="D186" s="12" t="s">
         <v>416</v>
       </c>
-      <c r="E186" s="7" t="s">
+      <c r="E186" s="12" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A187" s="7" t="s">
+      <c r="F186" s="5"/>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A187" s="12" t="s">
         <v>429</v>
       </c>
-      <c r="B187" s="7" t="s">
+      <c r="B187" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C187" s="7" t="s">
-        <v>284</v>
-      </c>
-      <c r="D187" s="7" t="s">
+      <c r="C187" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="D187" s="12" t="s">
         <v>423</v>
       </c>
-      <c r="E187" s="7" t="s">
+      <c r="E187" s="12" t="s">
         <v>430</v>
       </c>
-    </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A188" s="7">
+      <c r="F187" s="5"/>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A188" s="12">
         <v>628</v>
       </c>
-      <c r="B188" s="7" t="s">
+      <c r="B188" s="12" t="s">
         <v>425</v>
       </c>
-      <c r="C188" s="7" t="s">
-        <v>284</v>
-      </c>
-      <c r="D188" s="7" t="s">
+      <c r="C188" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="D188" s="12" t="s">
         <v>424</v>
       </c>
-      <c r="E188" s="7" t="s">
+      <c r="E188" s="12" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A189" s="7">
+      <c r="F188" s="5"/>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A189" s="12">
         <v>638</v>
       </c>
-      <c r="B189" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C189" s="7" t="s">
-        <v>284</v>
-      </c>
-      <c r="D189" s="7" t="s">
+      <c r="B189" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C189" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="D189" s="12" t="s">
         <v>426</v>
       </c>
-      <c r="E189" s="7" t="s">
+      <c r="E189" s="12" t="s">
         <v>432</v>
       </c>
-    </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A190" s="7">
+      <c r="F189" s="5"/>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A190" s="12">
         <v>640</v>
       </c>
-      <c r="B190" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C190" s="7" t="s">
-        <v>284</v>
-      </c>
-      <c r="D190" s="7" t="s">
+      <c r="B190" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C190" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="D190" s="12" t="s">
         <v>427</v>
       </c>
-      <c r="E190" s="7" t="s">
+      <c r="E190" s="12" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A191" s="7">
+      <c r="F190" s="5"/>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A191" s="12">
         <v>642</v>
       </c>
-      <c r="B191" s="7" t="s">
+      <c r="B191" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C191" s="7" t="s">
-        <v>284</v>
-      </c>
-      <c r="D191" s="7" t="s">
+      <c r="C191" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="D191" s="12" t="s">
         <v>428</v>
       </c>
-      <c r="E191" s="7" t="s">
+      <c r="E191" s="12" t="s">
         <v>434</v>
       </c>
-    </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A192" s="10">
+      <c r="F191" s="5"/>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A192" s="3">
         <v>660</v>
       </c>
-      <c r="B192" s="10" t="s">
+      <c r="B192" s="3" t="s">
         <v>435</v>
       </c>
-      <c r="C192" s="10"/>
-      <c r="D192" s="10" t="s">
+      <c r="C192" s="3"/>
+      <c r="D192" s="3" t="s">
         <v>436</v>
       </c>
-      <c r="E192" s="10" t="s">
+      <c r="E192" s="3" t="s">
         <v>437</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A193" s="10">
+      <c r="A193" s="3">
         <v>660</v>
       </c>
-      <c r="B193" s="10" t="s">
+      <c r="B193" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C193" s="10" t="s">
-        <v>283</v>
-      </c>
-      <c r="D193" s="10" t="s">
+      <c r="C193" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D193" s="3" t="s">
         <v>438</v>
       </c>
-      <c r="E193" s="10" t="s">
+      <c r="E193" s="3" t="s">
         <v>439</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A194" s="9">
+      <c r="A194" s="2">
         <v>661</v>
       </c>
-      <c r="B194" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C194" s="10" t="s">
-        <v>283</v>
-      </c>
-      <c r="D194" s="9" t="s">
+      <c r="B194" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C194" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D194" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="E194" s="9" t="s">
+      <c r="E194" s="2" t="s">
         <v>441</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A195" s="9">
+      <c r="A195" s="2">
         <v>663</v>
       </c>
-      <c r="B195" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C195" s="10" t="s">
-        <v>283</v>
-      </c>
-      <c r="D195" s="9" t="s">
+      <c r="B195" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C195" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D195" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="E195" s="9" t="s">
+      <c r="E195" s="2" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A196" s="9">
+      <c r="A196" s="2">
         <v>665</v>
       </c>
-      <c r="B196" s="9" t="s">
+      <c r="B196" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="C196" s="10"/>
-      <c r="D196" s="9" t="s">
+      <c r="C196" s="3"/>
+      <c r="D196" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="E196" s="9"/>
+      <c r="E196" s="2"/>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A197" s="9">
+      <c r="A197" s="2">
         <v>665</v>
       </c>
-      <c r="B197" s="9" t="s">
+      <c r="B197" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C197" s="10" t="s">
-        <v>283</v>
-      </c>
-      <c r="D197" s="10" t="s">
+      <c r="C197" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D197" s="3" t="s">
         <v>438</v>
       </c>
-      <c r="E197" s="10" t="s">
+      <c r="E197" s="3" t="s">
         <v>439</v>
       </c>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A198" s="9">
+      <c r="A198" s="2">
         <v>666</v>
       </c>
-      <c r="B198" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C198" s="10" t="s">
-        <v>283</v>
-      </c>
-      <c r="D198" s="9" t="s">
+      <c r="B198" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C198" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D198" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="E198" s="9" t="s">
+      <c r="E198" s="2" t="s">
         <v>441</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A199" s="9">
+      <c r="A199" s="2">
         <v>668</v>
       </c>
-      <c r="B199" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C199" s="10" t="s">
-        <v>283</v>
-      </c>
-      <c r="D199" s="9" t="s">
+      <c r="B199" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C199" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D199" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="E199" s="9" t="s">
+      <c r="E199" s="2" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A200" s="9">
+      <c r="A200" s="2">
         <v>670</v>
       </c>
-      <c r="B200" s="9" t="s">
+      <c r="B200" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="C200" s="10"/>
-      <c r="D200" s="9" t="s">
+      <c r="C200" s="3"/>
+      <c r="D200" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="E200" s="9"/>
+      <c r="E200" s="2"/>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A201" s="9">
+      <c r="A201" s="2">
         <v>670</v>
       </c>
-      <c r="B201" s="9" t="s">
+      <c r="B201" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C201" s="10" t="s">
-        <v>283</v>
-      </c>
-      <c r="D201" s="10" t="s">
+      <c r="C201" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D201" s="3" t="s">
         <v>438</v>
       </c>
-      <c r="E201" s="10" t="s">
+      <c r="E201" s="3" t="s">
         <v>439</v>
       </c>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A202" s="9">
+      <c r="A202" s="2">
         <v>671</v>
       </c>
-      <c r="B202" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C202" s="10" t="s">
-        <v>283</v>
-      </c>
-      <c r="D202" s="9" t="s">
+      <c r="B202" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C202" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D202" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="E202" s="9" t="s">
+      <c r="E202" s="2" t="s">
         <v>441</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A203" s="9">
+      <c r="A203" s="2">
         <v>673</v>
       </c>
-      <c r="B203" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C203" s="10" t="s">
-        <v>283</v>
-      </c>
-      <c r="D203" s="9" t="s">
+      <c r="B203" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C203" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D203" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="E203" s="9" t="s">
+      <c r="E203" s="2" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A204" s="9">
+      <c r="A204" s="2">
         <v>675</v>
       </c>
-      <c r="B204" s="9" t="s">
+      <c r="B204" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="C204" s="10"/>
-      <c r="D204" s="9" t="s">
+      <c r="C204" s="3"/>
+      <c r="D204" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="E204" s="9"/>
+      <c r="E204" s="2"/>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A205" s="9">
+      <c r="A205" s="2">
         <v>675</v>
       </c>
-      <c r="B205" s="9" t="s">
+      <c r="B205" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C205" s="10" t="s">
-        <v>283</v>
-      </c>
-      <c r="D205" s="10" t="s">
+      <c r="C205" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D205" s="3" t="s">
         <v>438</v>
       </c>
-      <c r="E205" s="10" t="s">
+      <c r="E205" s="3" t="s">
         <v>439</v>
       </c>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A206" s="9">
+      <c r="A206" s="2">
         <v>676</v>
       </c>
-      <c r="B206" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C206" s="10" t="s">
-        <v>283</v>
-      </c>
-      <c r="D206" s="9" t="s">
+      <c r="B206" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C206" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D206" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="E206" s="9" t="s">
+      <c r="E206" s="2" t="s">
         <v>441</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A207" s="9">
+      <c r="A207" s="2">
         <v>678</v>
       </c>
-      <c r="B207" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C207" s="10" t="s">
-        <v>283</v>
-      </c>
-      <c r="D207" s="9" t="s">
+      <c r="B207" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C207" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D207" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="E207" s="9" t="s">
+      <c r="E207" s="2" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A208" s="9" t="s">
+      <c r="A208" s="2" t="s">
         <v>447</v>
       </c>
-      <c r="B208" s="9" t="s">
+      <c r="B208" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C208" s="10" t="s">
-        <v>284</v>
-      </c>
-      <c r="D208" s="10" t="s">
+      <c r="C208" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D208" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="E208" s="9" t="s">
+      <c r="E208" s="2" t="s">
         <v>449</v>
       </c>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A209" s="9" t="s">
+      <c r="A209" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="B209" s="9" t="s">
+      <c r="B209" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C209" s="10" t="s">
-        <v>283</v>
-      </c>
-      <c r="D209" s="10" t="s">
+      <c r="C209" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D209" s="3" t="s">
         <v>451</v>
       </c>
-      <c r="E209" s="9" t="s">
+      <c r="E209" s="2" t="s">
         <v>452</v>
       </c>
+    </row>
+    <row r="210" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A210" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="B210" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C210" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D210" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="E210" s="3" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A211" s="6">
+        <v>1472</v>
+      </c>
+      <c r="B211" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C211" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D211" s="6" t="s">
+        <v>465</v>
+      </c>
+      <c r="E211" s="6" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A212" s="6">
+        <v>1480</v>
+      </c>
+      <c r="B212" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C212" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D212" s="6" t="s">
+        <v>466</v>
+      </c>
+      <c r="E212" s="6" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A213" s="6" t="s">
+        <v>474</v>
+      </c>
+      <c r="B213" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C213" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D213" s="6" t="s">
+        <v>467</v>
+      </c>
+      <c r="E213" s="6" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A214" s="6" t="s">
+        <v>475</v>
+      </c>
+      <c r="B214" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C214" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D214" s="6" t="s">
+        <v>467</v>
+      </c>
+      <c r="E214" s="6" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A215" s="6">
+        <v>1490</v>
+      </c>
+      <c r="B215" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C215" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D215" s="6" t="s">
+        <v>468</v>
+      </c>
+      <c r="E215" s="6" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A216" s="6">
+        <v>1494</v>
+      </c>
+      <c r="B216" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C216" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D216" s="6" t="s">
+        <v>469</v>
+      </c>
+      <c r="E216" s="6" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A217" s="6">
+        <v>1502</v>
+      </c>
+      <c r="B217" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C217" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D217" s="6" t="s">
+        <v>470</v>
+      </c>
+      <c r="E217" s="6" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A218" s="6">
+        <v>1506</v>
+      </c>
+      <c r="B218" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C218" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D218" s="6" t="s">
+        <v>471</v>
+      </c>
+      <c r="E218" s="6" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A219" s="6">
+        <v>1516</v>
+      </c>
+      <c r="B219" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C219" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D219" s="6" t="s">
+        <v>461</v>
+      </c>
+      <c r="E219" s="6" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A220" s="6">
+        <v>1520</v>
+      </c>
+      <c r="B220" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C220" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D220" s="6" t="s">
+        <v>462</v>
+      </c>
+      <c r="E220" s="6" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A221" s="6">
+        <v>1524</v>
+      </c>
+      <c r="B221" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C221" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D221" s="6" t="s">
+        <v>463</v>
+      </c>
+      <c r="E221" s="6" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A222" s="6">
+        <v>1528</v>
+      </c>
+      <c r="B222" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C222" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D222" s="6" t="s">
+        <v>464</v>
+      </c>
+      <c r="E222" s="6" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="225" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E225" s="3"/>
+    </row>
+    <row r="227" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E227" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="F150:F159"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="B71 B127:C128 C129:C141 B142:C142 B145:B159 D166:D180 B181:B186 B191 C194:C1048576">
-    <cfRule type="containsText" dxfId="11" priority="64" operator="containsText" text="Set">
-      <formula>NOT(ISERROR(SEARCH("Set",B71)))</formula>
+  <conditionalFormatting sqref="B71 B127:C128 C129:C141 B142:C142 B145:B159 D166:D180 B181:B186 B191 C269:C1048576 A235:A250 D210 A211:A222 C194:C218">
+    <cfRule type="containsText" dxfId="19" priority="75" operator="containsText" text="View">
+      <formula>NOT(ISERROR(SEARCH("View",A71)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="10" priority="63" operator="containsText" text="View">
-      <formula>NOT(ISERROR(SEARCH("View",B71)))</formula>
+    <cfRule type="containsText" dxfId="18" priority="76" operator="containsText" text="Set">
+      <formula>NOT(ISERROR(SEARCH("Set",A71)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B143:D143">
-    <cfRule type="containsText" dxfId="9" priority="59" operator="containsText" text="View">
+    <cfRule type="containsText" dxfId="17" priority="71" operator="containsText" text="View">
       <formula>NOT(ISERROR(SEARCH("View",B143)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="60" operator="containsText" text="Set">
+    <cfRule type="containsText" dxfId="16" priority="72" operator="containsText" text="Set">
       <formula>NOT(ISERROR(SEARCH("Set",B143)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C126">
-    <cfRule type="containsText" dxfId="7" priority="27" operator="containsText" text="View">
+    <cfRule type="containsText" dxfId="15" priority="39" operator="containsText" text="View">
       <formula>NOT(ISERROR(SEARCH("View",C1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="28" operator="containsText" text="Set">
+    <cfRule type="containsText" dxfId="14" priority="40" operator="containsText" text="Set">
       <formula>NOT(ISERROR(SEARCH("Set",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C144:C187">
-    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="View">
+    <cfRule type="containsText" dxfId="13" priority="13" operator="containsText" text="View">
       <formula>NOT(ISERROR(SEARCH("View",C144)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="Set">
+    <cfRule type="containsText" dxfId="12" priority="14" operator="containsText" text="Set">
       <formula>NOT(ISERROR(SEARCH("Set",C144)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C189:C191">
-    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="View">
+    <cfRule type="containsText" dxfId="11" priority="15" operator="containsText" text="View">
       <formula>NOT(ISERROR(SEARCH("View",C189)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="Set">
+    <cfRule type="containsText" dxfId="10" priority="16" operator="containsText" text="Set">
       <formula>NOT(ISERROR(SEARCH("Set",C189)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C188:D188">
-    <cfRule type="containsText" dxfId="1" priority="9" operator="containsText" text="View">
+    <cfRule type="containsText" dxfId="9" priority="21" operator="containsText" text="View">
       <formula>NOT(ISERROR(SEARCH("View",C188)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="10" operator="containsText" text="Set">
+    <cfRule type="containsText" dxfId="8" priority="22" operator="containsText" text="Set">
       <formula>NOT(ISERROR(SEARCH("Set",C188)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C219">
+    <cfRule type="containsText" dxfId="7" priority="7" operator="containsText" text="View">
+      <formula>NOT(ISERROR(SEARCH("View",C219)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="6" priority="8" operator="containsText" text="Set">
+      <formula>NOT(ISERROR(SEARCH("Set",C219)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C220">
+    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="View">
+      <formula>NOT(ISERROR(SEARCH("View",C220)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="6" operator="containsText" text="Set">
+      <formula>NOT(ISERROR(SEARCH("Set",C220)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C221">
+    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="View">
+      <formula>NOT(ISERROR(SEARCH("View",C221)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="Set">
+      <formula>NOT(ISERROR(SEARCH("Set",C221)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C222">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="View">
+      <formula>NOT(ISERROR(SEARCH("View",C222)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="Set">
+      <formula>NOT(ISERROR(SEARCH("Set",C222)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
